--- a/Docx/ProductBacklog-Nhom7.xlsx
+++ b/Docx/ProductBacklog-Nhom7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A7AE9D4-5B52-434B-99F0-554ED2C44662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9756614-111E-4E63-9182-32AAE49B30DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="186">
   <si>
     <t>STORY READER SYSTEM - SPRINT BACKLOG</t>
   </si>
@@ -260,9 +260,6 @@
     <t>Tuần 8</t>
   </si>
   <si>
-    <t>Đã xong Backend [x] | Quyền đọc chỉ kích hoạt SAU KHI thanh toán thành công</t>
-  </si>
-  <si>
     <t>PB16</t>
   </si>
   <si>
@@ -284,9 +281,6 @@
     <t>Purchase Story - Mua lẻ truyện, thanh toán một lần</t>
   </si>
   <si>
-    <t>Đã xong Backend [x] | Giao dịch thất bại thì không cấp quyền; quyền mua độc lập với gói</t>
-  </si>
-  <si>
     <t>Tổng điểm Sprint 3</t>
   </si>
   <si>
@@ -300,9 +294,6 @@
   </si>
   <si>
     <t>Tuần 9</t>
-  </si>
-  <si>
-    <t>Đã xong Backend [x] | Xử lý ca thanh toán thành công nhưng lỗi cập nhật quyền</t>
   </si>
   <si>
     <t>PB19</t>
@@ -1049,20 +1040,20 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1341,7 +1332,7 @@
     <row r="1" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1351,7 +1342,7 @@
     </row>
     <row r="4" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="35" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C4" s="36"/>
       <c r="D4" s="36"/>
@@ -1366,2678 +1357,2678 @@
       <c r="M4" s="36"/>
     </row>
     <row r="5" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="32"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="32"/>
-      <c r="K5" s="32"/>
-      <c r="L5" s="32"/>
-      <c r="M5" s="32"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="33"/>
+      <c r="M5" s="33"/>
     </row>
     <row r="6" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="32"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="32"/>
-      <c r="K6" s="32"/>
-      <c r="L6" s="32"/>
-      <c r="M6" s="32"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="33"/>
+      <c r="M6" s="33"/>
     </row>
     <row r="7" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="32"/>
-      <c r="K7" s="32"/>
-      <c r="L7" s="32"/>
-      <c r="M7" s="32"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="33"/>
+      <c r="J7" s="33"/>
+      <c r="K7" s="33"/>
+      <c r="L7" s="33"/>
+      <c r="M7" s="33"/>
     </row>
     <row r="8" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-      <c r="K8" s="32"/>
-      <c r="L8" s="32"/>
-      <c r="M8" s="32"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="33"/>
+      <c r="L8" s="33"/>
+      <c r="M8" s="33"/>
     </row>
     <row r="9" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-      <c r="K9" s="32"/>
-      <c r="L9" s="32"/>
-      <c r="M9" s="32"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="33"/>
+      <c r="J9" s="33"/>
+      <c r="K9" s="33"/>
+      <c r="L9" s="33"/>
+      <c r="M9" s="33"/>
     </row>
     <row r="10" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-      <c r="K10" s="32"/>
-      <c r="L10" s="32"/>
-      <c r="M10" s="32"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="33"/>
+      <c r="M10" s="33"/>
     </row>
     <row r="11" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="32"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-      <c r="K11" s="32"/>
-      <c r="L11" s="32"/>
-      <c r="M11" s="32"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="33"/>
+      <c r="M11" s="33"/>
     </row>
     <row r="12" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32"/>
-      <c r="K12" s="32"/>
-      <c r="L12" s="32"/>
-      <c r="M12" s="32"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="33"/>
+      <c r="L12" s="33"/>
+      <c r="M12" s="33"/>
     </row>
     <row r="13" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
-      <c r="L13" s="32"/>
-      <c r="M13" s="32"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="33"/>
+      <c r="K13" s="33"/>
+      <c r="L13" s="33"/>
+      <c r="M13" s="33"/>
     </row>
     <row r="14" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="32"/>
-      <c r="L14" s="32"/>
-      <c r="M14" s="32"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="33"/>
+      <c r="M14" s="33"/>
     </row>
     <row r="15" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="32"/>
-      <c r="L15" s="32"/>
-      <c r="M15" s="32"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="33"/>
+      <c r="L15" s="33"/>
+      <c r="M15" s="33"/>
     </row>
     <row r="16" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
-      <c r="K16" s="32"/>
-      <c r="L16" s="32"/>
-      <c r="M16" s="32"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="33"/>
     </row>
     <row r="17" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="32"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="32"/>
-      <c r="K17" s="32"/>
-      <c r="L17" s="32"/>
-      <c r="M17" s="32"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="33"/>
+      <c r="M17" s="33"/>
     </row>
     <row r="18" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="32"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32"/>
-      <c r="K18" s="32"/>
-      <c r="L18" s="32"/>
-      <c r="M18" s="32"/>
+      <c r="B18" s="33"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="33"/>
+      <c r="L18" s="33"/>
+      <c r="M18" s="33"/>
     </row>
     <row r="19" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="32"/>
-      <c r="K19" s="32"/>
-      <c r="L19" s="32"/>
-      <c r="M19" s="32"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="33"/>
+      <c r="M19" s="33"/>
     </row>
     <row r="20" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="32"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="32"/>
-      <c r="K20" s="32"/>
-      <c r="L20" s="32"/>
-      <c r="M20" s="32"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="33"/>
+      <c r="M20" s="33"/>
     </row>
     <row r="21" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
-      <c r="L21" s="32"/>
-      <c r="M21" s="32"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="33"/>
+      <c r="M21" s="33"/>
     </row>
     <row r="22" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="32"/>
-      <c r="C22" s="32"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="32"/>
-      <c r="K22" s="32"/>
-      <c r="L22" s="32"/>
-      <c r="M22" s="32"/>
+      <c r="B22" s="33"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="33"/>
     </row>
     <row r="23" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="32"/>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
-      <c r="L23" s="32"/>
-      <c r="M23" s="32"/>
+      <c r="B23" s="33"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="33"/>
+      <c r="H23" s="33"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="33"/>
+      <c r="M23" s="33"/>
     </row>
     <row r="24" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="32"/>
-      <c r="C24" s="32"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="32"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="32"/>
-      <c r="K24" s="32"/>
-      <c r="L24" s="32"/>
-      <c r="M24" s="32"/>
+      <c r="B24" s="33"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
     </row>
     <row r="25" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="32"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="32"/>
-      <c r="L25" s="32"/>
-      <c r="M25" s="32"/>
+      <c r="B25" s="33"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="33"/>
+      <c r="L25" s="33"/>
+      <c r="M25" s="33"/>
     </row>
     <row r="26" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="32"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="32"/>
-      <c r="L26" s="32"/>
-      <c r="M26" s="32"/>
+      <c r="B26" s="33"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="33"/>
     </row>
     <row r="27" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="32"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="32"/>
-      <c r="L27" s="32"/>
-      <c r="M27" s="32"/>
+      <c r="B27" s="33"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="33"/>
     </row>
     <row r="28" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="32"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="32"/>
-      <c r="I28" s="32"/>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
+      <c r="B28" s="33"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="33"/>
     </row>
     <row r="29" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="32"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="32"/>
-      <c r="K29" s="32"/>
-      <c r="L29" s="32"/>
-      <c r="M29" s="32"/>
+      <c r="B29" s="33"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="33"/>
+      <c r="M29" s="33"/>
     </row>
     <row r="30" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="32"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="32"/>
-      <c r="J30" s="32"/>
-      <c r="K30" s="32"/>
-      <c r="L30" s="32"/>
-      <c r="M30" s="32"/>
+      <c r="B30" s="33"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="33"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
+      <c r="K30" s="33"/>
+      <c r="L30" s="33"/>
+      <c r="M30" s="33"/>
     </row>
     <row r="31" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="32"/>
-      <c r="C31" s="32"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="32"/>
-      <c r="J31" s="32"/>
-      <c r="K31" s="32"/>
-      <c r="L31" s="32"/>
-      <c r="M31" s="32"/>
+      <c r="B31" s="33"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
+      <c r="J31" s="33"/>
+      <c r="K31" s="33"/>
+      <c r="L31" s="33"/>
+      <c r="M31" s="33"/>
     </row>
     <row r="32" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="32"/>
-      <c r="C32" s="32"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="32"/>
-      <c r="I32" s="32"/>
-      <c r="J32" s="32"/>
-      <c r="K32" s="32"/>
-      <c r="L32" s="32"/>
-      <c r="M32" s="32"/>
+      <c r="B32" s="33"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="33"/>
+      <c r="K32" s="33"/>
+      <c r="L32" s="33"/>
+      <c r="M32" s="33"/>
     </row>
     <row r="33" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="32"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="32"/>
-      <c r="K33" s="32"/>
-      <c r="L33" s="32"/>
-      <c r="M33" s="32"/>
+      <c r="B33" s="33"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="33"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="33"/>
+      <c r="K33" s="33"/>
+      <c r="L33" s="33"/>
+      <c r="M33" s="33"/>
     </row>
     <row r="34" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="32"/>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="32"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="32"/>
-      <c r="I34" s="32"/>
-      <c r="J34" s="32"/>
-      <c r="K34" s="32"/>
-      <c r="L34" s="32"/>
-      <c r="M34" s="32"/>
+      <c r="B34" s="33"/>
+      <c r="C34" s="33"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="33"/>
+      <c r="G34" s="33"/>
+      <c r="H34" s="33"/>
+      <c r="I34" s="33"/>
+      <c r="J34" s="33"/>
+      <c r="K34" s="33"/>
+      <c r="L34" s="33"/>
+      <c r="M34" s="33"/>
     </row>
     <row r="35" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="32"/>
-      <c r="C35" s="32"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="32"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
-      <c r="H35" s="32"/>
-      <c r="I35" s="32"/>
-      <c r="J35" s="32"/>
-      <c r="K35" s="32"/>
-      <c r="L35" s="32"/>
-      <c r="M35" s="32"/>
+      <c r="B35" s="33"/>
+      <c r="C35" s="33"/>
+      <c r="D35" s="33"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="33"/>
+      <c r="G35" s="33"/>
+      <c r="H35" s="33"/>
+      <c r="I35" s="33"/>
+      <c r="J35" s="33"/>
+      <c r="K35" s="33"/>
+      <c r="L35" s="33"/>
+      <c r="M35" s="33"/>
     </row>
     <row r="36" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="32"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="32"/>
-      <c r="J36" s="32"/>
-      <c r="K36" s="32"/>
-      <c r="L36" s="32"/>
-      <c r="M36" s="32"/>
+      <c r="B36" s="33"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="33"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="33"/>
+      <c r="K36" s="33"/>
+      <c r="L36" s="33"/>
+      <c r="M36" s="33"/>
     </row>
     <row r="37" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="32"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="32"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="32"/>
-      <c r="I37" s="32"/>
-      <c r="J37" s="32"/>
-      <c r="K37" s="32"/>
-      <c r="L37" s="32"/>
-      <c r="M37" s="32"/>
+      <c r="B37" s="33"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="33"/>
+      <c r="E37" s="33"/>
+      <c r="F37" s="33"/>
+      <c r="G37" s="33"/>
+      <c r="H37" s="33"/>
+      <c r="I37" s="33"/>
+      <c r="J37" s="33"/>
+      <c r="K37" s="33"/>
+      <c r="L37" s="33"/>
+      <c r="M37" s="33"/>
     </row>
     <row r="38" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="32"/>
-      <c r="C38" s="32"/>
-      <c r="D38" s="32"/>
-      <c r="E38" s="32"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="32"/>
-      <c r="H38" s="32"/>
-      <c r="I38" s="32"/>
-      <c r="J38" s="32"/>
-      <c r="K38" s="32"/>
-      <c r="L38" s="32"/>
-      <c r="M38" s="32"/>
+      <c r="B38" s="33"/>
+      <c r="C38" s="33"/>
+      <c r="D38" s="33"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="33"/>
+      <c r="H38" s="33"/>
+      <c r="I38" s="33"/>
+      <c r="J38" s="33"/>
+      <c r="K38" s="33"/>
+      <c r="L38" s="33"/>
+      <c r="M38" s="33"/>
     </row>
     <row r="39" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="32"/>
-      <c r="C39" s="32"/>
-      <c r="D39" s="32"/>
-      <c r="E39" s="32"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="32"/>
-      <c r="H39" s="32"/>
-      <c r="I39" s="32"/>
-      <c r="J39" s="32"/>
-      <c r="K39" s="32"/>
-      <c r="L39" s="32"/>
-      <c r="M39" s="32"/>
+      <c r="B39" s="33"/>
+      <c r="C39" s="33"/>
+      <c r="D39" s="33"/>
+      <c r="E39" s="33"/>
+      <c r="F39" s="33"/>
+      <c r="G39" s="33"/>
+      <c r="H39" s="33"/>
+      <c r="I39" s="33"/>
+      <c r="J39" s="33"/>
+      <c r="K39" s="33"/>
+      <c r="L39" s="33"/>
+      <c r="M39" s="33"/>
     </row>
     <row r="40" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="32"/>
-      <c r="C40" s="32"/>
-      <c r="D40" s="32"/>
-      <c r="E40" s="32"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="32"/>
-      <c r="H40" s="32"/>
-      <c r="I40" s="32"/>
-      <c r="J40" s="32"/>
-      <c r="K40" s="32"/>
-      <c r="L40" s="32"/>
-      <c r="M40" s="32"/>
+      <c r="B40" s="33"/>
+      <c r="C40" s="33"/>
+      <c r="D40" s="33"/>
+      <c r="E40" s="33"/>
+      <c r="F40" s="33"/>
+      <c r="G40" s="33"/>
+      <c r="H40" s="33"/>
+      <c r="I40" s="33"/>
+      <c r="J40" s="33"/>
+      <c r="K40" s="33"/>
+      <c r="L40" s="33"/>
+      <c r="M40" s="33"/>
     </row>
     <row r="41" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="32"/>
-      <c r="C41" s="32"/>
-      <c r="D41" s="32"/>
-      <c r="E41" s="32"/>
-      <c r="F41" s="32"/>
-      <c r="G41" s="32"/>
-      <c r="H41" s="32"/>
-      <c r="I41" s="32"/>
-      <c r="J41" s="32"/>
-      <c r="K41" s="32"/>
-      <c r="L41" s="32"/>
-      <c r="M41" s="32"/>
+      <c r="B41" s="33"/>
+      <c r="C41" s="33"/>
+      <c r="D41" s="33"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="33"/>
+      <c r="G41" s="33"/>
+      <c r="H41" s="33"/>
+      <c r="I41" s="33"/>
+      <c r="J41" s="33"/>
+      <c r="K41" s="33"/>
+      <c r="L41" s="33"/>
+      <c r="M41" s="33"/>
     </row>
     <row r="42" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="32"/>
-      <c r="C42" s="32"/>
-      <c r="D42" s="32"/>
-      <c r="E42" s="32"/>
-      <c r="F42" s="32"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="32"/>
-      <c r="I42" s="32"/>
-      <c r="J42" s="32"/>
-      <c r="K42" s="32"/>
-      <c r="L42" s="32"/>
-      <c r="M42" s="32"/>
+      <c r="B42" s="33"/>
+      <c r="C42" s="33"/>
+      <c r="D42" s="33"/>
+      <c r="E42" s="33"/>
+      <c r="F42" s="33"/>
+      <c r="G42" s="33"/>
+      <c r="H42" s="33"/>
+      <c r="I42" s="33"/>
+      <c r="J42" s="33"/>
+      <c r="K42" s="33"/>
+      <c r="L42" s="33"/>
+      <c r="M42" s="33"/>
     </row>
     <row r="43" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="32"/>
-      <c r="C43" s="32"/>
-      <c r="D43" s="32"/>
-      <c r="E43" s="32"/>
-      <c r="F43" s="32"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="32"/>
-      <c r="I43" s="32"/>
-      <c r="J43" s="32"/>
-      <c r="K43" s="32"/>
-      <c r="L43" s="32"/>
-      <c r="M43" s="32"/>
+      <c r="B43" s="33"/>
+      <c r="C43" s="33"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="33"/>
+      <c r="F43" s="33"/>
+      <c r="G43" s="33"/>
+      <c r="H43" s="33"/>
+      <c r="I43" s="33"/>
+      <c r="J43" s="33"/>
+      <c r="K43" s="33"/>
+      <c r="L43" s="33"/>
+      <c r="M43" s="33"/>
     </row>
     <row r="44" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="32"/>
-      <c r="C44" s="32"/>
-      <c r="D44" s="32"/>
-      <c r="E44" s="32"/>
-      <c r="F44" s="32"/>
-      <c r="G44" s="32"/>
-      <c r="H44" s="32"/>
-      <c r="I44" s="32"/>
-      <c r="J44" s="32"/>
-      <c r="K44" s="32"/>
-      <c r="L44" s="32"/>
-      <c r="M44" s="32"/>
+      <c r="B44" s="33"/>
+      <c r="C44" s="33"/>
+      <c r="D44" s="33"/>
+      <c r="E44" s="33"/>
+      <c r="F44" s="33"/>
+      <c r="G44" s="33"/>
+      <c r="H44" s="33"/>
+      <c r="I44" s="33"/>
+      <c r="J44" s="33"/>
+      <c r="K44" s="33"/>
+      <c r="L44" s="33"/>
+      <c r="M44" s="33"/>
     </row>
     <row r="45" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="32"/>
-      <c r="C45" s="32"/>
-      <c r="D45" s="32"/>
-      <c r="E45" s="32"/>
-      <c r="F45" s="32"/>
-      <c r="G45" s="32"/>
-      <c r="H45" s="32"/>
-      <c r="I45" s="32"/>
-      <c r="J45" s="32"/>
-      <c r="K45" s="32"/>
-      <c r="L45" s="32"/>
-      <c r="M45" s="32"/>
+      <c r="B45" s="33"/>
+      <c r="C45" s="33"/>
+      <c r="D45" s="33"/>
+      <c r="E45" s="33"/>
+      <c r="F45" s="33"/>
+      <c r="G45" s="33"/>
+      <c r="H45" s="33"/>
+      <c r="I45" s="33"/>
+      <c r="J45" s="33"/>
+      <c r="K45" s="33"/>
+      <c r="L45" s="33"/>
+      <c r="M45" s="33"/>
     </row>
     <row r="46" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="32"/>
-      <c r="C46" s="32"/>
-      <c r="D46" s="32"/>
-      <c r="E46" s="32"/>
-      <c r="F46" s="32"/>
-      <c r="G46" s="32"/>
-      <c r="H46" s="32"/>
-      <c r="I46" s="32"/>
-      <c r="J46" s="32"/>
-      <c r="K46" s="32"/>
-      <c r="L46" s="32"/>
-      <c r="M46" s="32"/>
+      <c r="B46" s="33"/>
+      <c r="C46" s="33"/>
+      <c r="D46" s="33"/>
+      <c r="E46" s="33"/>
+      <c r="F46" s="33"/>
+      <c r="G46" s="33"/>
+      <c r="H46" s="33"/>
+      <c r="I46" s="33"/>
+      <c r="J46" s="33"/>
+      <c r="K46" s="33"/>
+      <c r="L46" s="33"/>
+      <c r="M46" s="33"/>
     </row>
     <row r="47" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="32"/>
-      <c r="C47" s="32"/>
-      <c r="D47" s="32"/>
-      <c r="E47" s="32"/>
-      <c r="F47" s="32"/>
-      <c r="G47" s="32"/>
-      <c r="H47" s="32"/>
-      <c r="I47" s="32"/>
-      <c r="J47" s="32"/>
-      <c r="K47" s="32"/>
-      <c r="L47" s="32"/>
-      <c r="M47" s="32"/>
+      <c r="B47" s="33"/>
+      <c r="C47" s="33"/>
+      <c r="D47" s="33"/>
+      <c r="E47" s="33"/>
+      <c r="F47" s="33"/>
+      <c r="G47" s="33"/>
+      <c r="H47" s="33"/>
+      <c r="I47" s="33"/>
+      <c r="J47" s="33"/>
+      <c r="K47" s="33"/>
+      <c r="L47" s="33"/>
+      <c r="M47" s="33"/>
     </row>
     <row r="48" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="32"/>
-      <c r="C48" s="32"/>
-      <c r="D48" s="32"/>
-      <c r="E48" s="32"/>
-      <c r="F48" s="32"/>
-      <c r="G48" s="32"/>
-      <c r="H48" s="32"/>
-      <c r="I48" s="32"/>
-      <c r="J48" s="32"/>
-      <c r="K48" s="32"/>
-      <c r="L48" s="32"/>
-      <c r="M48" s="32"/>
+      <c r="B48" s="33"/>
+      <c r="C48" s="33"/>
+      <c r="D48" s="33"/>
+      <c r="E48" s="33"/>
+      <c r="F48" s="33"/>
+      <c r="G48" s="33"/>
+      <c r="H48" s="33"/>
+      <c r="I48" s="33"/>
+      <c r="J48" s="33"/>
+      <c r="K48" s="33"/>
+      <c r="L48" s="33"/>
+      <c r="M48" s="33"/>
     </row>
     <row r="49" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="32"/>
-      <c r="C49" s="32"/>
-      <c r="D49" s="32"/>
-      <c r="E49" s="32"/>
-      <c r="F49" s="32"/>
-      <c r="G49" s="32"/>
-      <c r="H49" s="32"/>
-      <c r="I49" s="32"/>
-      <c r="J49" s="32"/>
-      <c r="K49" s="32"/>
-      <c r="L49" s="32"/>
-      <c r="M49" s="32"/>
+      <c r="B49" s="33"/>
+      <c r="C49" s="33"/>
+      <c r="D49" s="33"/>
+      <c r="E49" s="33"/>
+      <c r="F49" s="33"/>
+      <c r="G49" s="33"/>
+      <c r="H49" s="33"/>
+      <c r="I49" s="33"/>
+      <c r="J49" s="33"/>
+      <c r="K49" s="33"/>
+      <c r="L49" s="33"/>
+      <c r="M49" s="33"/>
     </row>
     <row r="50" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="32"/>
-      <c r="C50" s="32"/>
-      <c r="D50" s="32"/>
-      <c r="E50" s="32"/>
-      <c r="F50" s="32"/>
-      <c r="G50" s="32"/>
-      <c r="H50" s="32"/>
-      <c r="I50" s="32"/>
-      <c r="J50" s="32"/>
-      <c r="K50" s="32"/>
-      <c r="L50" s="32"/>
-      <c r="M50" s="32"/>
+      <c r="B50" s="33"/>
+      <c r="C50" s="33"/>
+      <c r="D50" s="33"/>
+      <c r="E50" s="33"/>
+      <c r="F50" s="33"/>
+      <c r="G50" s="33"/>
+      <c r="H50" s="33"/>
+      <c r="I50" s="33"/>
+      <c r="J50" s="33"/>
+      <c r="K50" s="33"/>
+      <c r="L50" s="33"/>
+      <c r="M50" s="33"/>
     </row>
     <row r="51" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="32"/>
-      <c r="C51" s="32"/>
-      <c r="D51" s="32"/>
-      <c r="E51" s="32"/>
-      <c r="F51" s="32"/>
-      <c r="G51" s="32"/>
-      <c r="H51" s="32"/>
-      <c r="I51" s="32"/>
-      <c r="J51" s="32"/>
-      <c r="K51" s="32"/>
-      <c r="L51" s="32"/>
-      <c r="M51" s="32"/>
+      <c r="B51" s="33"/>
+      <c r="C51" s="33"/>
+      <c r="D51" s="33"/>
+      <c r="E51" s="33"/>
+      <c r="F51" s="33"/>
+      <c r="G51" s="33"/>
+      <c r="H51" s="33"/>
+      <c r="I51" s="33"/>
+      <c r="J51" s="33"/>
+      <c r="K51" s="33"/>
+      <c r="L51" s="33"/>
+      <c r="M51" s="33"/>
     </row>
     <row r="52" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="32"/>
-      <c r="C52" s="32"/>
-      <c r="D52" s="32"/>
-      <c r="E52" s="32"/>
-      <c r="F52" s="32"/>
-      <c r="G52" s="32"/>
-      <c r="H52" s="32"/>
-      <c r="I52" s="32"/>
-      <c r="J52" s="32"/>
-      <c r="K52" s="32"/>
-      <c r="L52" s="32"/>
-      <c r="M52" s="32"/>
+      <c r="B52" s="33"/>
+      <c r="C52" s="33"/>
+      <c r="D52" s="33"/>
+      <c r="E52" s="33"/>
+      <c r="F52" s="33"/>
+      <c r="G52" s="33"/>
+      <c r="H52" s="33"/>
+      <c r="I52" s="33"/>
+      <c r="J52" s="33"/>
+      <c r="K52" s="33"/>
+      <c r="L52" s="33"/>
+      <c r="M52" s="33"/>
     </row>
     <row r="53" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="32"/>
-      <c r="C53" s="32"/>
-      <c r="D53" s="32"/>
-      <c r="E53" s="32"/>
-      <c r="F53" s="32"/>
-      <c r="G53" s="32"/>
-      <c r="H53" s="32"/>
-      <c r="I53" s="32"/>
-      <c r="J53" s="32"/>
-      <c r="K53" s="32"/>
-      <c r="L53" s="32"/>
-      <c r="M53" s="32"/>
+      <c r="B53" s="33"/>
+      <c r="C53" s="33"/>
+      <c r="D53" s="33"/>
+      <c r="E53" s="33"/>
+      <c r="F53" s="33"/>
+      <c r="G53" s="33"/>
+      <c r="H53" s="33"/>
+      <c r="I53" s="33"/>
+      <c r="J53" s="33"/>
+      <c r="K53" s="33"/>
+      <c r="L53" s="33"/>
+      <c r="M53" s="33"/>
     </row>
     <row r="54" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="32"/>
-      <c r="C54" s="32"/>
-      <c r="D54" s="32"/>
-      <c r="E54" s="32"/>
-      <c r="F54" s="32"/>
-      <c r="G54" s="32"/>
-      <c r="H54" s="32"/>
-      <c r="I54" s="32"/>
-      <c r="J54" s="32"/>
-      <c r="K54" s="32"/>
-      <c r="L54" s="32"/>
-      <c r="M54" s="32"/>
+      <c r="B54" s="33"/>
+      <c r="C54" s="33"/>
+      <c r="D54" s="33"/>
+      <c r="E54" s="33"/>
+      <c r="F54" s="33"/>
+      <c r="G54" s="33"/>
+      <c r="H54" s="33"/>
+      <c r="I54" s="33"/>
+      <c r="J54" s="33"/>
+      <c r="K54" s="33"/>
+      <c r="L54" s="33"/>
+      <c r="M54" s="33"/>
     </row>
     <row r="55" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="32"/>
-      <c r="C55" s="32"/>
-      <c r="D55" s="32"/>
-      <c r="E55" s="32"/>
-      <c r="F55" s="32"/>
-      <c r="G55" s="32"/>
-      <c r="H55" s="32"/>
-      <c r="I55" s="32"/>
-      <c r="J55" s="32"/>
-      <c r="K55" s="32"/>
-      <c r="L55" s="32"/>
-      <c r="M55" s="32"/>
+      <c r="B55" s="33"/>
+      <c r="C55" s="33"/>
+      <c r="D55" s="33"/>
+      <c r="E55" s="33"/>
+      <c r="F55" s="33"/>
+      <c r="G55" s="33"/>
+      <c r="H55" s="33"/>
+      <c r="I55" s="33"/>
+      <c r="J55" s="33"/>
+      <c r="K55" s="33"/>
+      <c r="L55" s="33"/>
+      <c r="M55" s="33"/>
     </row>
     <row r="56" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="32"/>
-      <c r="C56" s="32"/>
-      <c r="D56" s="32"/>
-      <c r="E56" s="32"/>
-      <c r="F56" s="32"/>
-      <c r="G56" s="32"/>
-      <c r="H56" s="32"/>
-      <c r="I56" s="32"/>
-      <c r="J56" s="32"/>
-      <c r="K56" s="32"/>
-      <c r="L56" s="32"/>
-      <c r="M56" s="32"/>
+      <c r="B56" s="33"/>
+      <c r="C56" s="33"/>
+      <c r="D56" s="33"/>
+      <c r="E56" s="33"/>
+      <c r="F56" s="33"/>
+      <c r="G56" s="33"/>
+      <c r="H56" s="33"/>
+      <c r="I56" s="33"/>
+      <c r="J56" s="33"/>
+      <c r="K56" s="33"/>
+      <c r="L56" s="33"/>
+      <c r="M56" s="33"/>
     </row>
     <row r="57" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="32"/>
-      <c r="C57" s="32"/>
-      <c r="D57" s="32"/>
-      <c r="E57" s="32"/>
-      <c r="F57" s="32"/>
-      <c r="G57" s="32"/>
-      <c r="H57" s="32"/>
-      <c r="I57" s="32"/>
-      <c r="J57" s="32"/>
-      <c r="K57" s="32"/>
-      <c r="L57" s="32"/>
-      <c r="M57" s="32"/>
+      <c r="B57" s="33"/>
+      <c r="C57" s="33"/>
+      <c r="D57" s="33"/>
+      <c r="E57" s="33"/>
+      <c r="F57" s="33"/>
+      <c r="G57" s="33"/>
+      <c r="H57" s="33"/>
+      <c r="I57" s="33"/>
+      <c r="J57" s="33"/>
+      <c r="K57" s="33"/>
+      <c r="L57" s="33"/>
+      <c r="M57" s="33"/>
     </row>
     <row r="58" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="32"/>
-      <c r="C58" s="32"/>
-      <c r="D58" s="32"/>
-      <c r="E58" s="32"/>
-      <c r="F58" s="32"/>
-      <c r="G58" s="32"/>
-      <c r="H58" s="32"/>
-      <c r="I58" s="32"/>
-      <c r="J58" s="32"/>
-      <c r="K58" s="32"/>
-      <c r="L58" s="32"/>
-      <c r="M58" s="32"/>
+      <c r="B58" s="33"/>
+      <c r="C58" s="33"/>
+      <c r="D58" s="33"/>
+      <c r="E58" s="33"/>
+      <c r="F58" s="33"/>
+      <c r="G58" s="33"/>
+      <c r="H58" s="33"/>
+      <c r="I58" s="33"/>
+      <c r="J58" s="33"/>
+      <c r="K58" s="33"/>
+      <c r="L58" s="33"/>
+      <c r="M58" s="33"/>
     </row>
     <row r="59" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="32"/>
-      <c r="C59" s="32"/>
-      <c r="D59" s="32"/>
-      <c r="E59" s="32"/>
-      <c r="F59" s="32"/>
-      <c r="G59" s="32"/>
-      <c r="H59" s="32"/>
-      <c r="I59" s="32"/>
-      <c r="J59" s="32"/>
-      <c r="K59" s="32"/>
-      <c r="L59" s="32"/>
-      <c r="M59" s="32"/>
+      <c r="B59" s="33"/>
+      <c r="C59" s="33"/>
+      <c r="D59" s="33"/>
+      <c r="E59" s="33"/>
+      <c r="F59" s="33"/>
+      <c r="G59" s="33"/>
+      <c r="H59" s="33"/>
+      <c r="I59" s="33"/>
+      <c r="J59" s="33"/>
+      <c r="K59" s="33"/>
+      <c r="L59" s="33"/>
+      <c r="M59" s="33"/>
     </row>
     <row r="60" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="32"/>
-      <c r="C60" s="32"/>
-      <c r="D60" s="32"/>
-      <c r="E60" s="32"/>
-      <c r="F60" s="32"/>
-      <c r="G60" s="32"/>
-      <c r="H60" s="32"/>
-      <c r="I60" s="32"/>
-      <c r="J60" s="32"/>
-      <c r="K60" s="32"/>
-      <c r="L60" s="32"/>
-      <c r="M60" s="32"/>
+      <c r="B60" s="33"/>
+      <c r="C60" s="33"/>
+      <c r="D60" s="33"/>
+      <c r="E60" s="33"/>
+      <c r="F60" s="33"/>
+      <c r="G60" s="33"/>
+      <c r="H60" s="33"/>
+      <c r="I60" s="33"/>
+      <c r="J60" s="33"/>
+      <c r="K60" s="33"/>
+      <c r="L60" s="33"/>
+      <c r="M60" s="33"/>
     </row>
     <row r="61" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="32"/>
-      <c r="C61" s="32"/>
-      <c r="D61" s="32"/>
-      <c r="E61" s="32"/>
-      <c r="F61" s="32"/>
-      <c r="G61" s="32"/>
-      <c r="H61" s="32"/>
-      <c r="I61" s="32"/>
-      <c r="J61" s="32"/>
-      <c r="K61" s="32"/>
-      <c r="L61" s="32"/>
-      <c r="M61" s="32"/>
+      <c r="B61" s="33"/>
+      <c r="C61" s="33"/>
+      <c r="D61" s="33"/>
+      <c r="E61" s="33"/>
+      <c r="F61" s="33"/>
+      <c r="G61" s="33"/>
+      <c r="H61" s="33"/>
+      <c r="I61" s="33"/>
+      <c r="J61" s="33"/>
+      <c r="K61" s="33"/>
+      <c r="L61" s="33"/>
+      <c r="M61" s="33"/>
     </row>
     <row r="62" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="32"/>
-      <c r="C62" s="32"/>
-      <c r="D62" s="32"/>
-      <c r="E62" s="32"/>
-      <c r="F62" s="32"/>
-      <c r="G62" s="32"/>
-      <c r="H62" s="32"/>
-      <c r="I62" s="32"/>
-      <c r="J62" s="32"/>
-      <c r="K62" s="32"/>
-      <c r="L62" s="32"/>
-      <c r="M62" s="32"/>
+      <c r="B62" s="33"/>
+      <c r="C62" s="33"/>
+      <c r="D62" s="33"/>
+      <c r="E62" s="33"/>
+      <c r="F62" s="33"/>
+      <c r="G62" s="33"/>
+      <c r="H62" s="33"/>
+      <c r="I62" s="33"/>
+      <c r="J62" s="33"/>
+      <c r="K62" s="33"/>
+      <c r="L62" s="33"/>
+      <c r="M62" s="33"/>
     </row>
     <row r="63" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="32"/>
-      <c r="C63" s="32"/>
-      <c r="D63" s="32"/>
-      <c r="E63" s="32"/>
-      <c r="F63" s="32"/>
-      <c r="G63" s="32"/>
-      <c r="H63" s="32"/>
-      <c r="I63" s="32"/>
-      <c r="J63" s="32"/>
-      <c r="K63" s="32"/>
-      <c r="L63" s="32"/>
-      <c r="M63" s="32"/>
+      <c r="B63" s="33"/>
+      <c r="C63" s="33"/>
+      <c r="D63" s="33"/>
+      <c r="E63" s="33"/>
+      <c r="F63" s="33"/>
+      <c r="G63" s="33"/>
+      <c r="H63" s="33"/>
+      <c r="I63" s="33"/>
+      <c r="J63" s="33"/>
+      <c r="K63" s="33"/>
+      <c r="L63" s="33"/>
+      <c r="M63" s="33"/>
     </row>
     <row r="64" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="32"/>
-      <c r="C64" s="32"/>
-      <c r="D64" s="32"/>
-      <c r="E64" s="32"/>
-      <c r="F64" s="32"/>
-      <c r="G64" s="32"/>
-      <c r="H64" s="32"/>
-      <c r="I64" s="32"/>
-      <c r="J64" s="32"/>
-      <c r="K64" s="32"/>
-      <c r="L64" s="32"/>
-      <c r="M64" s="32"/>
+      <c r="B64" s="33"/>
+      <c r="C64" s="33"/>
+      <c r="D64" s="33"/>
+      <c r="E64" s="33"/>
+      <c r="F64" s="33"/>
+      <c r="G64" s="33"/>
+      <c r="H64" s="33"/>
+      <c r="I64" s="33"/>
+      <c r="J64" s="33"/>
+      <c r="K64" s="33"/>
+      <c r="L64" s="33"/>
+      <c r="M64" s="33"/>
     </row>
     <row r="65" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="32"/>
-      <c r="C65" s="32"/>
-      <c r="D65" s="32"/>
-      <c r="E65" s="32"/>
-      <c r="F65" s="32"/>
-      <c r="G65" s="32"/>
-      <c r="H65" s="32"/>
-      <c r="I65" s="32"/>
-      <c r="J65" s="32"/>
-      <c r="K65" s="32"/>
-      <c r="L65" s="32"/>
-      <c r="M65" s="32"/>
+      <c r="B65" s="33"/>
+      <c r="C65" s="33"/>
+      <c r="D65" s="33"/>
+      <c r="E65" s="33"/>
+      <c r="F65" s="33"/>
+      <c r="G65" s="33"/>
+      <c r="H65" s="33"/>
+      <c r="I65" s="33"/>
+      <c r="J65" s="33"/>
+      <c r="K65" s="33"/>
+      <c r="L65" s="33"/>
+      <c r="M65" s="33"/>
     </row>
     <row r="66" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="32"/>
-      <c r="C66" s="32"/>
-      <c r="D66" s="32"/>
-      <c r="E66" s="32"/>
-      <c r="F66" s="32"/>
-      <c r="G66" s="32"/>
-      <c r="H66" s="32"/>
-      <c r="I66" s="32"/>
-      <c r="J66" s="32"/>
-      <c r="K66" s="32"/>
-      <c r="L66" s="32"/>
-      <c r="M66" s="32"/>
+      <c r="B66" s="33"/>
+      <c r="C66" s="33"/>
+      <c r="D66" s="33"/>
+      <c r="E66" s="33"/>
+      <c r="F66" s="33"/>
+      <c r="G66" s="33"/>
+      <c r="H66" s="33"/>
+      <c r="I66" s="33"/>
+      <c r="J66" s="33"/>
+      <c r="K66" s="33"/>
+      <c r="L66" s="33"/>
+      <c r="M66" s="33"/>
     </row>
     <row r="67" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="32"/>
-      <c r="C67" s="32"/>
-      <c r="D67" s="32"/>
-      <c r="E67" s="32"/>
-      <c r="F67" s="32"/>
-      <c r="G67" s="32"/>
-      <c r="H67" s="32"/>
-      <c r="I67" s="32"/>
-      <c r="J67" s="32"/>
-      <c r="K67" s="32"/>
-      <c r="L67" s="32"/>
-      <c r="M67" s="32"/>
+      <c r="B67" s="33"/>
+      <c r="C67" s="33"/>
+      <c r="D67" s="33"/>
+      <c r="E67" s="33"/>
+      <c r="F67" s="33"/>
+      <c r="G67" s="33"/>
+      <c r="H67" s="33"/>
+      <c r="I67" s="33"/>
+      <c r="J67" s="33"/>
+      <c r="K67" s="33"/>
+      <c r="L67" s="33"/>
+      <c r="M67" s="33"/>
     </row>
     <row r="68" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="32"/>
-      <c r="C68" s="32"/>
-      <c r="D68" s="32"/>
-      <c r="E68" s="32"/>
-      <c r="F68" s="32"/>
-      <c r="G68" s="32"/>
-      <c r="H68" s="32"/>
-      <c r="I68" s="32"/>
-      <c r="J68" s="32"/>
-      <c r="K68" s="32"/>
-      <c r="L68" s="32"/>
-      <c r="M68" s="32"/>
+      <c r="B68" s="33"/>
+      <c r="C68" s="33"/>
+      <c r="D68" s="33"/>
+      <c r="E68" s="33"/>
+      <c r="F68" s="33"/>
+      <c r="G68" s="33"/>
+      <c r="H68" s="33"/>
+      <c r="I68" s="33"/>
+      <c r="J68" s="33"/>
+      <c r="K68" s="33"/>
+      <c r="L68" s="33"/>
+      <c r="M68" s="33"/>
     </row>
     <row r="69" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="32"/>
-      <c r="C69" s="32"/>
-      <c r="D69" s="32"/>
-      <c r="E69" s="32"/>
-      <c r="F69" s="32"/>
-      <c r="G69" s="32"/>
-      <c r="H69" s="32"/>
-      <c r="I69" s="32"/>
-      <c r="J69" s="32"/>
-      <c r="K69" s="32"/>
-      <c r="L69" s="32"/>
-      <c r="M69" s="32"/>
+      <c r="B69" s="33"/>
+      <c r="C69" s="33"/>
+      <c r="D69" s="33"/>
+      <c r="E69" s="33"/>
+      <c r="F69" s="33"/>
+      <c r="G69" s="33"/>
+      <c r="H69" s="33"/>
+      <c r="I69" s="33"/>
+      <c r="J69" s="33"/>
+      <c r="K69" s="33"/>
+      <c r="L69" s="33"/>
+      <c r="M69" s="33"/>
     </row>
     <row r="70" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="32"/>
-      <c r="C70" s="32"/>
-      <c r="D70" s="32"/>
-      <c r="E70" s="32"/>
-      <c r="F70" s="32"/>
-      <c r="G70" s="32"/>
-      <c r="H70" s="32"/>
-      <c r="I70" s="32"/>
-      <c r="J70" s="32"/>
-      <c r="K70" s="32"/>
-      <c r="L70" s="32"/>
-      <c r="M70" s="32"/>
+      <c r="B70" s="33"/>
+      <c r="C70" s="33"/>
+      <c r="D70" s="33"/>
+      <c r="E70" s="33"/>
+      <c r="F70" s="33"/>
+      <c r="G70" s="33"/>
+      <c r="H70" s="33"/>
+      <c r="I70" s="33"/>
+      <c r="J70" s="33"/>
+      <c r="K70" s="33"/>
+      <c r="L70" s="33"/>
+      <c r="M70" s="33"/>
     </row>
     <row r="71" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="32"/>
-      <c r="C71" s="32"/>
-      <c r="D71" s="32"/>
-      <c r="E71" s="32"/>
-      <c r="F71" s="32"/>
-      <c r="G71" s="32"/>
-      <c r="H71" s="32"/>
-      <c r="I71" s="32"/>
-      <c r="J71" s="32"/>
-      <c r="K71" s="32"/>
-      <c r="L71" s="32"/>
-      <c r="M71" s="32"/>
+      <c r="B71" s="33"/>
+      <c r="C71" s="33"/>
+      <c r="D71" s="33"/>
+      <c r="E71" s="33"/>
+      <c r="F71" s="33"/>
+      <c r="G71" s="33"/>
+      <c r="H71" s="33"/>
+      <c r="I71" s="33"/>
+      <c r="J71" s="33"/>
+      <c r="K71" s="33"/>
+      <c r="L71" s="33"/>
+      <c r="M71" s="33"/>
     </row>
     <row r="72" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="32"/>
-      <c r="C72" s="32"/>
-      <c r="D72" s="32"/>
-      <c r="E72" s="32"/>
-      <c r="F72" s="32"/>
-      <c r="G72" s="32"/>
-      <c r="H72" s="32"/>
-      <c r="I72" s="32"/>
-      <c r="J72" s="32"/>
-      <c r="K72" s="32"/>
-      <c r="L72" s="32"/>
-      <c r="M72" s="32"/>
+      <c r="B72" s="33"/>
+      <c r="C72" s="33"/>
+      <c r="D72" s="33"/>
+      <c r="E72" s="33"/>
+      <c r="F72" s="33"/>
+      <c r="G72" s="33"/>
+      <c r="H72" s="33"/>
+      <c r="I72" s="33"/>
+      <c r="J72" s="33"/>
+      <c r="K72" s="33"/>
+      <c r="L72" s="33"/>
+      <c r="M72" s="33"/>
     </row>
     <row r="73" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="32"/>
-      <c r="C73" s="32"/>
-      <c r="D73" s="32"/>
-      <c r="E73" s="32"/>
-      <c r="F73" s="32"/>
-      <c r="G73" s="32"/>
-      <c r="H73" s="32"/>
-      <c r="I73" s="32"/>
-      <c r="J73" s="32"/>
-      <c r="K73" s="32"/>
-      <c r="L73" s="32"/>
-      <c r="M73" s="32"/>
+      <c r="B73" s="33"/>
+      <c r="C73" s="33"/>
+      <c r="D73" s="33"/>
+      <c r="E73" s="33"/>
+      <c r="F73" s="33"/>
+      <c r="G73" s="33"/>
+      <c r="H73" s="33"/>
+      <c r="I73" s="33"/>
+      <c r="J73" s="33"/>
+      <c r="K73" s="33"/>
+      <c r="L73" s="33"/>
+      <c r="M73" s="33"/>
     </row>
     <row r="74" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="32"/>
-      <c r="C74" s="32"/>
-      <c r="D74" s="32"/>
-      <c r="E74" s="32"/>
-      <c r="F74" s="32"/>
-      <c r="G74" s="32"/>
-      <c r="H74" s="32"/>
-      <c r="I74" s="32"/>
-      <c r="J74" s="32"/>
-      <c r="K74" s="32"/>
-      <c r="L74" s="32"/>
-      <c r="M74" s="32"/>
+      <c r="B74" s="33"/>
+      <c r="C74" s="33"/>
+      <c r="D74" s="33"/>
+      <c r="E74" s="33"/>
+      <c r="F74" s="33"/>
+      <c r="G74" s="33"/>
+      <c r="H74" s="33"/>
+      <c r="I74" s="33"/>
+      <c r="J74" s="33"/>
+      <c r="K74" s="33"/>
+      <c r="L74" s="33"/>
+      <c r="M74" s="33"/>
     </row>
     <row r="75" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="32"/>
-      <c r="C75" s="32"/>
-      <c r="D75" s="32"/>
-      <c r="E75" s="32"/>
-      <c r="F75" s="32"/>
-      <c r="G75" s="32"/>
-      <c r="H75" s="32"/>
-      <c r="I75" s="32"/>
-      <c r="J75" s="32"/>
-      <c r="K75" s="32"/>
-      <c r="L75" s="32"/>
-      <c r="M75" s="32"/>
+      <c r="B75" s="33"/>
+      <c r="C75" s="33"/>
+      <c r="D75" s="33"/>
+      <c r="E75" s="33"/>
+      <c r="F75" s="33"/>
+      <c r="G75" s="33"/>
+      <c r="H75" s="33"/>
+      <c r="I75" s="33"/>
+      <c r="J75" s="33"/>
+      <c r="K75" s="33"/>
+      <c r="L75" s="33"/>
+      <c r="M75" s="33"/>
     </row>
     <row r="76" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="32"/>
-      <c r="C76" s="32"/>
-      <c r="D76" s="32"/>
-      <c r="E76" s="32"/>
-      <c r="F76" s="32"/>
-      <c r="G76" s="32"/>
-      <c r="H76" s="32"/>
-      <c r="I76" s="32"/>
-      <c r="J76" s="32"/>
-      <c r="K76" s="32"/>
-      <c r="L76" s="32"/>
-      <c r="M76" s="32"/>
+      <c r="B76" s="33"/>
+      <c r="C76" s="33"/>
+      <c r="D76" s="33"/>
+      <c r="E76" s="33"/>
+      <c r="F76" s="33"/>
+      <c r="G76" s="33"/>
+      <c r="H76" s="33"/>
+      <c r="I76" s="33"/>
+      <c r="J76" s="33"/>
+      <c r="K76" s="33"/>
+      <c r="L76" s="33"/>
+      <c r="M76" s="33"/>
     </row>
     <row r="77" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="32"/>
-      <c r="C77" s="32"/>
-      <c r="D77" s="32"/>
-      <c r="E77" s="32"/>
-      <c r="F77" s="32"/>
-      <c r="G77" s="32"/>
-      <c r="H77" s="32"/>
-      <c r="I77" s="32"/>
-      <c r="J77" s="32"/>
-      <c r="K77" s="32"/>
-      <c r="L77" s="32"/>
-      <c r="M77" s="32"/>
+      <c r="B77" s="33"/>
+      <c r="C77" s="33"/>
+      <c r="D77" s="33"/>
+      <c r="E77" s="33"/>
+      <c r="F77" s="33"/>
+      <c r="G77" s="33"/>
+      <c r="H77" s="33"/>
+      <c r="I77" s="33"/>
+      <c r="J77" s="33"/>
+      <c r="K77" s="33"/>
+      <c r="L77" s="33"/>
+      <c r="M77" s="33"/>
     </row>
     <row r="78" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="32"/>
-      <c r="C78" s="32"/>
-      <c r="D78" s="32"/>
-      <c r="E78" s="32"/>
-      <c r="F78" s="32"/>
-      <c r="G78" s="32"/>
-      <c r="H78" s="32"/>
-      <c r="I78" s="32"/>
-      <c r="J78" s="32"/>
-      <c r="K78" s="32"/>
-      <c r="L78" s="32"/>
-      <c r="M78" s="32"/>
+      <c r="B78" s="33"/>
+      <c r="C78" s="33"/>
+      <c r="D78" s="33"/>
+      <c r="E78" s="33"/>
+      <c r="F78" s="33"/>
+      <c r="G78" s="33"/>
+      <c r="H78" s="33"/>
+      <c r="I78" s="33"/>
+      <c r="J78" s="33"/>
+      <c r="K78" s="33"/>
+      <c r="L78" s="33"/>
+      <c r="M78" s="33"/>
     </row>
     <row r="79" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="32"/>
-      <c r="C79" s="32"/>
-      <c r="D79" s="32"/>
-      <c r="E79" s="32"/>
-      <c r="F79" s="32"/>
-      <c r="G79" s="32"/>
-      <c r="H79" s="32"/>
-      <c r="I79" s="32"/>
-      <c r="J79" s="32"/>
-      <c r="K79" s="32"/>
-      <c r="L79" s="32"/>
-      <c r="M79" s="32"/>
+      <c r="B79" s="33"/>
+      <c r="C79" s="33"/>
+      <c r="D79" s="33"/>
+      <c r="E79" s="33"/>
+      <c r="F79" s="33"/>
+      <c r="G79" s="33"/>
+      <c r="H79" s="33"/>
+      <c r="I79" s="33"/>
+      <c r="J79" s="33"/>
+      <c r="K79" s="33"/>
+      <c r="L79" s="33"/>
+      <c r="M79" s="33"/>
     </row>
     <row r="80" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B80" s="32"/>
-      <c r="C80" s="32"/>
-      <c r="D80" s="32"/>
-      <c r="E80" s="32"/>
-      <c r="F80" s="32"/>
-      <c r="G80" s="32"/>
-      <c r="H80" s="32"/>
-      <c r="I80" s="32"/>
-      <c r="J80" s="32"/>
-      <c r="K80" s="32"/>
-      <c r="L80" s="32"/>
-      <c r="M80" s="32"/>
+      <c r="B80" s="33"/>
+      <c r="C80" s="33"/>
+      <c r="D80" s="33"/>
+      <c r="E80" s="33"/>
+      <c r="F80" s="33"/>
+      <c r="G80" s="33"/>
+      <c r="H80" s="33"/>
+      <c r="I80" s="33"/>
+      <c r="J80" s="33"/>
+      <c r="K80" s="33"/>
+      <c r="L80" s="33"/>
+      <c r="M80" s="33"/>
     </row>
     <row r="81" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="32"/>
-      <c r="C81" s="32"/>
-      <c r="D81" s="32"/>
-      <c r="E81" s="32"/>
-      <c r="F81" s="32"/>
-      <c r="G81" s="32"/>
-      <c r="H81" s="32"/>
-      <c r="I81" s="32"/>
-      <c r="J81" s="32"/>
-      <c r="K81" s="32"/>
-      <c r="L81" s="32"/>
-      <c r="M81" s="32"/>
+      <c r="B81" s="33"/>
+      <c r="C81" s="33"/>
+      <c r="D81" s="33"/>
+      <c r="E81" s="33"/>
+      <c r="F81" s="33"/>
+      <c r="G81" s="33"/>
+      <c r="H81" s="33"/>
+      <c r="I81" s="33"/>
+      <c r="J81" s="33"/>
+      <c r="K81" s="33"/>
+      <c r="L81" s="33"/>
+      <c r="M81" s="33"/>
     </row>
     <row r="82" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B82" s="32"/>
-      <c r="C82" s="32"/>
-      <c r="D82" s="32"/>
-      <c r="E82" s="32"/>
-      <c r="F82" s="32"/>
-      <c r="G82" s="32"/>
-      <c r="H82" s="32"/>
-      <c r="I82" s="32"/>
-      <c r="J82" s="32"/>
-      <c r="K82" s="32"/>
-      <c r="L82" s="32"/>
-      <c r="M82" s="32"/>
+      <c r="B82" s="33"/>
+      <c r="C82" s="33"/>
+      <c r="D82" s="33"/>
+      <c r="E82" s="33"/>
+      <c r="F82" s="33"/>
+      <c r="G82" s="33"/>
+      <c r="H82" s="33"/>
+      <c r="I82" s="33"/>
+      <c r="J82" s="33"/>
+      <c r="K82" s="33"/>
+      <c r="L82" s="33"/>
+      <c r="M82" s="33"/>
     </row>
     <row r="83" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="32"/>
-      <c r="C83" s="32"/>
-      <c r="D83" s="32"/>
-      <c r="E83" s="32"/>
-      <c r="F83" s="32"/>
-      <c r="G83" s="32"/>
-      <c r="H83" s="32"/>
-      <c r="I83" s="32"/>
-      <c r="J83" s="32"/>
-      <c r="K83" s="32"/>
-      <c r="L83" s="32"/>
-      <c r="M83" s="32"/>
+      <c r="B83" s="33"/>
+      <c r="C83" s="33"/>
+      <c r="D83" s="33"/>
+      <c r="E83" s="33"/>
+      <c r="F83" s="33"/>
+      <c r="G83" s="33"/>
+      <c r="H83" s="33"/>
+      <c r="I83" s="33"/>
+      <c r="J83" s="33"/>
+      <c r="K83" s="33"/>
+      <c r="L83" s="33"/>
+      <c r="M83" s="33"/>
     </row>
     <row r="84" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="32"/>
-      <c r="C84" s="32"/>
-      <c r="D84" s="32"/>
-      <c r="E84" s="32"/>
-      <c r="F84" s="32"/>
-      <c r="G84" s="32"/>
-      <c r="H84" s="32"/>
-      <c r="I84" s="32"/>
-      <c r="J84" s="32"/>
-      <c r="K84" s="32"/>
-      <c r="L84" s="32"/>
-      <c r="M84" s="32"/>
+      <c r="B84" s="33"/>
+      <c r="C84" s="33"/>
+      <c r="D84" s="33"/>
+      <c r="E84" s="33"/>
+      <c r="F84" s="33"/>
+      <c r="G84" s="33"/>
+      <c r="H84" s="33"/>
+      <c r="I84" s="33"/>
+      <c r="J84" s="33"/>
+      <c r="K84" s="33"/>
+      <c r="L84" s="33"/>
+      <c r="M84" s="33"/>
     </row>
     <row r="85" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="32"/>
-      <c r="C85" s="32"/>
-      <c r="D85" s="32"/>
-      <c r="E85" s="32"/>
-      <c r="F85" s="32"/>
-      <c r="G85" s="32"/>
-      <c r="H85" s="32"/>
-      <c r="I85" s="32"/>
-      <c r="J85" s="32"/>
-      <c r="K85" s="32"/>
-      <c r="L85" s="32"/>
-      <c r="M85" s="32"/>
+      <c r="B85" s="33"/>
+      <c r="C85" s="33"/>
+      <c r="D85" s="33"/>
+      <c r="E85" s="33"/>
+      <c r="F85" s="33"/>
+      <c r="G85" s="33"/>
+      <c r="H85" s="33"/>
+      <c r="I85" s="33"/>
+      <c r="J85" s="33"/>
+      <c r="K85" s="33"/>
+      <c r="L85" s="33"/>
+      <c r="M85" s="33"/>
     </row>
     <row r="86" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="32"/>
-      <c r="C86" s="32"/>
-      <c r="D86" s="32"/>
-      <c r="E86" s="32"/>
-      <c r="F86" s="32"/>
-      <c r="G86" s="32"/>
-      <c r="H86" s="32"/>
-      <c r="I86" s="32"/>
-      <c r="J86" s="32"/>
-      <c r="K86" s="32"/>
-      <c r="L86" s="32"/>
-      <c r="M86" s="32"/>
+      <c r="B86" s="33"/>
+      <c r="C86" s="33"/>
+      <c r="D86" s="33"/>
+      <c r="E86" s="33"/>
+      <c r="F86" s="33"/>
+      <c r="G86" s="33"/>
+      <c r="H86" s="33"/>
+      <c r="I86" s="33"/>
+      <c r="J86" s="33"/>
+      <c r="K86" s="33"/>
+      <c r="L86" s="33"/>
+      <c r="M86" s="33"/>
     </row>
     <row r="87" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="32"/>
-      <c r="C87" s="32"/>
-      <c r="D87" s="32"/>
-      <c r="E87" s="32"/>
-      <c r="F87" s="32"/>
-      <c r="G87" s="32"/>
-      <c r="H87" s="32"/>
-      <c r="I87" s="32"/>
-      <c r="J87" s="32"/>
-      <c r="K87" s="32"/>
-      <c r="L87" s="32"/>
-      <c r="M87" s="32"/>
+      <c r="B87" s="33"/>
+      <c r="C87" s="33"/>
+      <c r="D87" s="33"/>
+      <c r="E87" s="33"/>
+      <c r="F87" s="33"/>
+      <c r="G87" s="33"/>
+      <c r="H87" s="33"/>
+      <c r="I87" s="33"/>
+      <c r="J87" s="33"/>
+      <c r="K87" s="33"/>
+      <c r="L87" s="33"/>
+      <c r="M87" s="33"/>
     </row>
     <row r="88" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="32"/>
-      <c r="C88" s="32"/>
-      <c r="D88" s="32"/>
-      <c r="E88" s="32"/>
-      <c r="F88" s="32"/>
-      <c r="G88" s="32"/>
-      <c r="H88" s="32"/>
-      <c r="I88" s="32"/>
-      <c r="J88" s="32"/>
-      <c r="K88" s="32"/>
-      <c r="L88" s="32"/>
-      <c r="M88" s="32"/>
+      <c r="B88" s="33"/>
+      <c r="C88" s="33"/>
+      <c r="D88" s="33"/>
+      <c r="E88" s="33"/>
+      <c r="F88" s="33"/>
+      <c r="G88" s="33"/>
+      <c r="H88" s="33"/>
+      <c r="I88" s="33"/>
+      <c r="J88" s="33"/>
+      <c r="K88" s="33"/>
+      <c r="L88" s="33"/>
+      <c r="M88" s="33"/>
     </row>
     <row r="89" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B89" s="32"/>
-      <c r="C89" s="32"/>
-      <c r="D89" s="32"/>
-      <c r="E89" s="32"/>
-      <c r="F89" s="32"/>
-      <c r="G89" s="32"/>
-      <c r="H89" s="32"/>
-      <c r="I89" s="32"/>
-      <c r="J89" s="32"/>
-      <c r="K89" s="32"/>
-      <c r="L89" s="32"/>
-      <c r="M89" s="32"/>
+      <c r="B89" s="33"/>
+      <c r="C89" s="33"/>
+      <c r="D89" s="33"/>
+      <c r="E89" s="33"/>
+      <c r="F89" s="33"/>
+      <c r="G89" s="33"/>
+      <c r="H89" s="33"/>
+      <c r="I89" s="33"/>
+      <c r="J89" s="33"/>
+      <c r="K89" s="33"/>
+      <c r="L89" s="33"/>
+      <c r="M89" s="33"/>
     </row>
     <row r="90" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B90" s="32"/>
-      <c r="C90" s="32"/>
-      <c r="D90" s="32"/>
-      <c r="E90" s="32"/>
-      <c r="F90" s="32"/>
-      <c r="G90" s="32"/>
-      <c r="H90" s="32"/>
-      <c r="I90" s="32"/>
-      <c r="J90" s="32"/>
-      <c r="K90" s="32"/>
-      <c r="L90" s="32"/>
-      <c r="M90" s="32"/>
+      <c r="B90" s="33"/>
+      <c r="C90" s="33"/>
+      <c r="D90" s="33"/>
+      <c r="E90" s="33"/>
+      <c r="F90" s="33"/>
+      <c r="G90" s="33"/>
+      <c r="H90" s="33"/>
+      <c r="I90" s="33"/>
+      <c r="J90" s="33"/>
+      <c r="K90" s="33"/>
+      <c r="L90" s="33"/>
+      <c r="M90" s="33"/>
     </row>
     <row r="91" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B91" s="32"/>
-      <c r="C91" s="32"/>
-      <c r="D91" s="32"/>
-      <c r="E91" s="32"/>
-      <c r="F91" s="32"/>
-      <c r="G91" s="32"/>
-      <c r="H91" s="32"/>
-      <c r="I91" s="32"/>
-      <c r="J91" s="32"/>
-      <c r="K91" s="32"/>
-      <c r="L91" s="32"/>
-      <c r="M91" s="32"/>
+      <c r="B91" s="33"/>
+      <c r="C91" s="33"/>
+      <c r="D91" s="33"/>
+      <c r="E91" s="33"/>
+      <c r="F91" s="33"/>
+      <c r="G91" s="33"/>
+      <c r="H91" s="33"/>
+      <c r="I91" s="33"/>
+      <c r="J91" s="33"/>
+      <c r="K91" s="33"/>
+      <c r="L91" s="33"/>
+      <c r="M91" s="33"/>
     </row>
     <row r="92" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B92" s="32"/>
-      <c r="C92" s="32"/>
-      <c r="D92" s="32"/>
-      <c r="E92" s="32"/>
-      <c r="F92" s="32"/>
-      <c r="G92" s="32"/>
-      <c r="H92" s="32"/>
-      <c r="I92" s="32"/>
-      <c r="J92" s="32"/>
-      <c r="K92" s="32"/>
-      <c r="L92" s="32"/>
-      <c r="M92" s="32"/>
+      <c r="B92" s="33"/>
+      <c r="C92" s="33"/>
+      <c r="D92" s="33"/>
+      <c r="E92" s="33"/>
+      <c r="F92" s="33"/>
+      <c r="G92" s="33"/>
+      <c r="H92" s="33"/>
+      <c r="I92" s="33"/>
+      <c r="J92" s="33"/>
+      <c r="K92" s="33"/>
+      <c r="L92" s="33"/>
+      <c r="M92" s="33"/>
     </row>
     <row r="93" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B93" s="32"/>
-      <c r="C93" s="32"/>
-      <c r="D93" s="32"/>
-      <c r="E93" s="32"/>
-      <c r="F93" s="32"/>
-      <c r="G93" s="32"/>
-      <c r="H93" s="32"/>
-      <c r="I93" s="32"/>
-      <c r="J93" s="32"/>
-      <c r="K93" s="32"/>
-      <c r="L93" s="32"/>
-      <c r="M93" s="32"/>
+      <c r="B93" s="33"/>
+      <c r="C93" s="33"/>
+      <c r="D93" s="33"/>
+      <c r="E93" s="33"/>
+      <c r="F93" s="33"/>
+      <c r="G93" s="33"/>
+      <c r="H93" s="33"/>
+      <c r="I93" s="33"/>
+      <c r="J93" s="33"/>
+      <c r="K93" s="33"/>
+      <c r="L93" s="33"/>
+      <c r="M93" s="33"/>
     </row>
     <row r="94" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B94" s="32"/>
-      <c r="C94" s="32"/>
-      <c r="D94" s="32"/>
-      <c r="E94" s="32"/>
-      <c r="F94" s="32"/>
-      <c r="G94" s="32"/>
-      <c r="H94" s="32"/>
-      <c r="I94" s="32"/>
-      <c r="J94" s="32"/>
-      <c r="K94" s="32"/>
-      <c r="L94" s="32"/>
-      <c r="M94" s="32"/>
+      <c r="B94" s="33"/>
+      <c r="C94" s="33"/>
+      <c r="D94" s="33"/>
+      <c r="E94" s="33"/>
+      <c r="F94" s="33"/>
+      <c r="G94" s="33"/>
+      <c r="H94" s="33"/>
+      <c r="I94" s="33"/>
+      <c r="J94" s="33"/>
+      <c r="K94" s="33"/>
+      <c r="L94" s="33"/>
+      <c r="M94" s="33"/>
     </row>
     <row r="95" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="32"/>
-      <c r="C95" s="32"/>
-      <c r="D95" s="32"/>
-      <c r="E95" s="32"/>
-      <c r="F95" s="32"/>
-      <c r="G95" s="32"/>
-      <c r="H95" s="32"/>
-      <c r="I95" s="32"/>
-      <c r="J95" s="32"/>
-      <c r="K95" s="32"/>
-      <c r="L95" s="32"/>
-      <c r="M95" s="32"/>
+      <c r="B95" s="33"/>
+      <c r="C95" s="33"/>
+      <c r="D95" s="33"/>
+      <c r="E95" s="33"/>
+      <c r="F95" s="33"/>
+      <c r="G95" s="33"/>
+      <c r="H95" s="33"/>
+      <c r="I95" s="33"/>
+      <c r="J95" s="33"/>
+      <c r="K95" s="33"/>
+      <c r="L95" s="33"/>
+      <c r="M95" s="33"/>
     </row>
     <row r="96" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B96" s="32"/>
-      <c r="C96" s="32"/>
-      <c r="D96" s="32"/>
-      <c r="E96" s="32"/>
-      <c r="F96" s="32"/>
-      <c r="G96" s="32"/>
-      <c r="H96" s="32"/>
-      <c r="I96" s="32"/>
-      <c r="J96" s="32"/>
-      <c r="K96" s="32"/>
-      <c r="L96" s="32"/>
-      <c r="M96" s="32"/>
+      <c r="B96" s="33"/>
+      <c r="C96" s="33"/>
+      <c r="D96" s="33"/>
+      <c r="E96" s="33"/>
+      <c r="F96" s="33"/>
+      <c r="G96" s="33"/>
+      <c r="H96" s="33"/>
+      <c r="I96" s="33"/>
+      <c r="J96" s="33"/>
+      <c r="K96" s="33"/>
+      <c r="L96" s="33"/>
+      <c r="M96" s="33"/>
     </row>
     <row r="97" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B97" s="32"/>
-      <c r="C97" s="32"/>
-      <c r="D97" s="32"/>
-      <c r="E97" s="32"/>
-      <c r="F97" s="32"/>
-      <c r="G97" s="32"/>
-      <c r="H97" s="32"/>
-      <c r="I97" s="32"/>
-      <c r="J97" s="32"/>
-      <c r="K97" s="32"/>
-      <c r="L97" s="32"/>
-      <c r="M97" s="32"/>
+      <c r="B97" s="33"/>
+      <c r="C97" s="33"/>
+      <c r="D97" s="33"/>
+      <c r="E97" s="33"/>
+      <c r="F97" s="33"/>
+      <c r="G97" s="33"/>
+      <c r="H97" s="33"/>
+      <c r="I97" s="33"/>
+      <c r="J97" s="33"/>
+      <c r="K97" s="33"/>
+      <c r="L97" s="33"/>
+      <c r="M97" s="33"/>
     </row>
     <row r="98" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B98" s="32"/>
-      <c r="C98" s="32"/>
-      <c r="D98" s="32"/>
-      <c r="E98" s="32"/>
-      <c r="F98" s="32"/>
-      <c r="G98" s="32"/>
-      <c r="H98" s="32"/>
-      <c r="I98" s="32"/>
-      <c r="J98" s="32"/>
-      <c r="K98" s="32"/>
-      <c r="L98" s="32"/>
-      <c r="M98" s="32"/>
+      <c r="B98" s="33"/>
+      <c r="C98" s="33"/>
+      <c r="D98" s="33"/>
+      <c r="E98" s="33"/>
+      <c r="F98" s="33"/>
+      <c r="G98" s="33"/>
+      <c r="H98" s="33"/>
+      <c r="I98" s="33"/>
+      <c r="J98" s="33"/>
+      <c r="K98" s="33"/>
+      <c r="L98" s="33"/>
+      <c r="M98" s="33"/>
     </row>
     <row r="99" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B99" s="32"/>
-      <c r="C99" s="32"/>
-      <c r="D99" s="32"/>
-      <c r="E99" s="32"/>
-      <c r="F99" s="32"/>
-      <c r="G99" s="32"/>
-      <c r="H99" s="32"/>
-      <c r="I99" s="32"/>
-      <c r="J99" s="32"/>
-      <c r="K99" s="32"/>
-      <c r="L99" s="32"/>
-      <c r="M99" s="32"/>
+      <c r="B99" s="33"/>
+      <c r="C99" s="33"/>
+      <c r="D99" s="33"/>
+      <c r="E99" s="33"/>
+      <c r="F99" s="33"/>
+      <c r="G99" s="33"/>
+      <c r="H99" s="33"/>
+      <c r="I99" s="33"/>
+      <c r="J99" s="33"/>
+      <c r="K99" s="33"/>
+      <c r="L99" s="33"/>
+      <c r="M99" s="33"/>
     </row>
     <row r="100" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B100" s="32"/>
-      <c r="C100" s="32"/>
-      <c r="D100" s="32"/>
-      <c r="E100" s="32"/>
-      <c r="F100" s="32"/>
-      <c r="G100" s="32"/>
-      <c r="H100" s="32"/>
-      <c r="I100" s="32"/>
-      <c r="J100" s="32"/>
-      <c r="K100" s="32"/>
-      <c r="L100" s="32"/>
-      <c r="M100" s="32"/>
+      <c r="B100" s="33"/>
+      <c r="C100" s="33"/>
+      <c r="D100" s="33"/>
+      <c r="E100" s="33"/>
+      <c r="F100" s="33"/>
+      <c r="G100" s="33"/>
+      <c r="H100" s="33"/>
+      <c r="I100" s="33"/>
+      <c r="J100" s="33"/>
+      <c r="K100" s="33"/>
+      <c r="L100" s="33"/>
+      <c r="M100" s="33"/>
     </row>
     <row r="101" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B101" s="32"/>
-      <c r="C101" s="32"/>
-      <c r="D101" s="32"/>
-      <c r="E101" s="32"/>
-      <c r="F101" s="32"/>
-      <c r="G101" s="32"/>
-      <c r="H101" s="32"/>
-      <c r="I101" s="32"/>
-      <c r="J101" s="32"/>
-      <c r="K101" s="32"/>
-      <c r="L101" s="32"/>
-      <c r="M101" s="32"/>
+      <c r="B101" s="33"/>
+      <c r="C101" s="33"/>
+      <c r="D101" s="33"/>
+      <c r="E101" s="33"/>
+      <c r="F101" s="33"/>
+      <c r="G101" s="33"/>
+      <c r="H101" s="33"/>
+      <c r="I101" s="33"/>
+      <c r="J101" s="33"/>
+      <c r="K101" s="33"/>
+      <c r="L101" s="33"/>
+      <c r="M101" s="33"/>
     </row>
     <row r="102" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B102" s="32"/>
-      <c r="C102" s="32"/>
-      <c r="D102" s="32"/>
-      <c r="E102" s="32"/>
-      <c r="F102" s="32"/>
-      <c r="G102" s="32"/>
-      <c r="H102" s="32"/>
-      <c r="I102" s="32"/>
-      <c r="J102" s="32"/>
-      <c r="K102" s="32"/>
-      <c r="L102" s="32"/>
-      <c r="M102" s="32"/>
+      <c r="B102" s="33"/>
+      <c r="C102" s="33"/>
+      <c r="D102" s="33"/>
+      <c r="E102" s="33"/>
+      <c r="F102" s="33"/>
+      <c r="G102" s="33"/>
+      <c r="H102" s="33"/>
+      <c r="I102" s="33"/>
+      <c r="J102" s="33"/>
+      <c r="K102" s="33"/>
+      <c r="L102" s="33"/>
+      <c r="M102" s="33"/>
     </row>
     <row r="103" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B103" s="32"/>
-      <c r="C103" s="32"/>
-      <c r="D103" s="32"/>
-      <c r="E103" s="32"/>
-      <c r="F103" s="32"/>
-      <c r="G103" s="32"/>
-      <c r="H103" s="32"/>
-      <c r="I103" s="32"/>
-      <c r="J103" s="32"/>
-      <c r="K103" s="32"/>
-      <c r="L103" s="32"/>
-      <c r="M103" s="32"/>
+      <c r="B103" s="33"/>
+      <c r="C103" s="33"/>
+      <c r="D103" s="33"/>
+      <c r="E103" s="33"/>
+      <c r="F103" s="33"/>
+      <c r="G103" s="33"/>
+      <c r="H103" s="33"/>
+      <c r="I103" s="33"/>
+      <c r="J103" s="33"/>
+      <c r="K103" s="33"/>
+      <c r="L103" s="33"/>
+      <c r="M103" s="33"/>
     </row>
     <row r="104" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B104" s="32"/>
-      <c r="C104" s="32"/>
-      <c r="D104" s="32"/>
-      <c r="E104" s="32"/>
-      <c r="F104" s="32"/>
-      <c r="G104" s="32"/>
-      <c r="H104" s="32"/>
-      <c r="I104" s="32"/>
-      <c r="J104" s="32"/>
-      <c r="K104" s="32"/>
-      <c r="L104" s="32"/>
-      <c r="M104" s="32"/>
+      <c r="B104" s="33"/>
+      <c r="C104" s="33"/>
+      <c r="D104" s="33"/>
+      <c r="E104" s="33"/>
+      <c r="F104" s="33"/>
+      <c r="G104" s="33"/>
+      <c r="H104" s="33"/>
+      <c r="I104" s="33"/>
+      <c r="J104" s="33"/>
+      <c r="K104" s="33"/>
+      <c r="L104" s="33"/>
+      <c r="M104" s="33"/>
     </row>
     <row r="105" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B105" s="32"/>
-      <c r="C105" s="32"/>
-      <c r="D105" s="32"/>
-      <c r="E105" s="32"/>
-      <c r="F105" s="32"/>
-      <c r="G105" s="32"/>
-      <c r="H105" s="32"/>
-      <c r="I105" s="32"/>
-      <c r="J105" s="32"/>
-      <c r="K105" s="32"/>
-      <c r="L105" s="32"/>
-      <c r="M105" s="32"/>
+      <c r="B105" s="33"/>
+      <c r="C105" s="33"/>
+      <c r="D105" s="33"/>
+      <c r="E105" s="33"/>
+      <c r="F105" s="33"/>
+      <c r="G105" s="33"/>
+      <c r="H105" s="33"/>
+      <c r="I105" s="33"/>
+      <c r="J105" s="33"/>
+      <c r="K105" s="33"/>
+      <c r="L105" s="33"/>
+      <c r="M105" s="33"/>
     </row>
     <row r="106" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B106" s="32"/>
-      <c r="C106" s="32"/>
-      <c r="D106" s="32"/>
-      <c r="E106" s="32"/>
-      <c r="F106" s="32"/>
-      <c r="G106" s="32"/>
-      <c r="H106" s="32"/>
-      <c r="I106" s="32"/>
-      <c r="J106" s="32"/>
-      <c r="K106" s="32"/>
-      <c r="L106" s="32"/>
-      <c r="M106" s="32"/>
+      <c r="B106" s="33"/>
+      <c r="C106" s="33"/>
+      <c r="D106" s="33"/>
+      <c r="E106" s="33"/>
+      <c r="F106" s="33"/>
+      <c r="G106" s="33"/>
+      <c r="H106" s="33"/>
+      <c r="I106" s="33"/>
+      <c r="J106" s="33"/>
+      <c r="K106" s="33"/>
+      <c r="L106" s="33"/>
+      <c r="M106" s="33"/>
     </row>
     <row r="107" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B107" s="32"/>
-      <c r="C107" s="32"/>
-      <c r="D107" s="32"/>
-      <c r="E107" s="32"/>
-      <c r="F107" s="32"/>
-      <c r="G107" s="32"/>
-      <c r="H107" s="32"/>
-      <c r="I107" s="32"/>
-      <c r="J107" s="32"/>
-      <c r="K107" s="32"/>
-      <c r="L107" s="32"/>
-      <c r="M107" s="32"/>
+      <c r="B107" s="33"/>
+      <c r="C107" s="33"/>
+      <c r="D107" s="33"/>
+      <c r="E107" s="33"/>
+      <c r="F107" s="33"/>
+      <c r="G107" s="33"/>
+      <c r="H107" s="33"/>
+      <c r="I107" s="33"/>
+      <c r="J107" s="33"/>
+      <c r="K107" s="33"/>
+      <c r="L107" s="33"/>
+      <c r="M107" s="33"/>
     </row>
     <row r="108" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B108" s="32"/>
-      <c r="C108" s="32"/>
-      <c r="D108" s="32"/>
-      <c r="E108" s="32"/>
-      <c r="F108" s="32"/>
-      <c r="G108" s="32"/>
-      <c r="H108" s="32"/>
-      <c r="I108" s="32"/>
-      <c r="J108" s="32"/>
-      <c r="K108" s="32"/>
-      <c r="L108" s="32"/>
-      <c r="M108" s="32"/>
+      <c r="B108" s="33"/>
+      <c r="C108" s="33"/>
+      <c r="D108" s="33"/>
+      <c r="E108" s="33"/>
+      <c r="F108" s="33"/>
+      <c r="G108" s="33"/>
+      <c r="H108" s="33"/>
+      <c r="I108" s="33"/>
+      <c r="J108" s="33"/>
+      <c r="K108" s="33"/>
+      <c r="L108" s="33"/>
+      <c r="M108" s="33"/>
     </row>
     <row r="109" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B109" s="32"/>
-      <c r="C109" s="32"/>
-      <c r="D109" s="32"/>
-      <c r="E109" s="32"/>
-      <c r="F109" s="32"/>
-      <c r="G109" s="32"/>
-      <c r="H109" s="32"/>
-      <c r="I109" s="32"/>
-      <c r="J109" s="32"/>
-      <c r="K109" s="32"/>
-      <c r="L109" s="32"/>
-      <c r="M109" s="32"/>
+      <c r="B109" s="33"/>
+      <c r="C109" s="33"/>
+      <c r="D109" s="33"/>
+      <c r="E109" s="33"/>
+      <c r="F109" s="33"/>
+      <c r="G109" s="33"/>
+      <c r="H109" s="33"/>
+      <c r="I109" s="33"/>
+      <c r="J109" s="33"/>
+      <c r="K109" s="33"/>
+      <c r="L109" s="33"/>
+      <c r="M109" s="33"/>
     </row>
     <row r="110" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B110" s="32"/>
-      <c r="C110" s="32"/>
-      <c r="D110" s="32"/>
-      <c r="E110" s="32"/>
-      <c r="F110" s="32"/>
-      <c r="G110" s="32"/>
-      <c r="H110" s="32"/>
-      <c r="I110" s="32"/>
-      <c r="J110" s="32"/>
-      <c r="K110" s="32"/>
-      <c r="L110" s="32"/>
-      <c r="M110" s="32"/>
+      <c r="B110" s="33"/>
+      <c r="C110" s="33"/>
+      <c r="D110" s="33"/>
+      <c r="E110" s="33"/>
+      <c r="F110" s="33"/>
+      <c r="G110" s="33"/>
+      <c r="H110" s="33"/>
+      <c r="I110" s="33"/>
+      <c r="J110" s="33"/>
+      <c r="K110" s="33"/>
+      <c r="L110" s="33"/>
+      <c r="M110" s="33"/>
     </row>
     <row r="111" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B111" s="32"/>
-      <c r="C111" s="32"/>
-      <c r="D111" s="32"/>
-      <c r="E111" s="32"/>
-      <c r="F111" s="32"/>
-      <c r="G111" s="32"/>
-      <c r="H111" s="32"/>
-      <c r="I111" s="32"/>
-      <c r="J111" s="32"/>
-      <c r="K111" s="32"/>
-      <c r="L111" s="32"/>
-      <c r="M111" s="32"/>
+      <c r="B111" s="33"/>
+      <c r="C111" s="33"/>
+      <c r="D111" s="33"/>
+      <c r="E111" s="33"/>
+      <c r="F111" s="33"/>
+      <c r="G111" s="33"/>
+      <c r="H111" s="33"/>
+      <c r="I111" s="33"/>
+      <c r="J111" s="33"/>
+      <c r="K111" s="33"/>
+      <c r="L111" s="33"/>
+      <c r="M111" s="33"/>
     </row>
     <row r="112" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B112" s="32"/>
-      <c r="C112" s="32"/>
-      <c r="D112" s="32"/>
-      <c r="E112" s="32"/>
-      <c r="F112" s="32"/>
-      <c r="G112" s="32"/>
-      <c r="H112" s="32"/>
-      <c r="I112" s="32"/>
-      <c r="J112" s="32"/>
-      <c r="K112" s="32"/>
-      <c r="L112" s="32"/>
-      <c r="M112" s="32"/>
+      <c r="B112" s="33"/>
+      <c r="C112" s="33"/>
+      <c r="D112" s="33"/>
+      <c r="E112" s="33"/>
+      <c r="F112" s="33"/>
+      <c r="G112" s="33"/>
+      <c r="H112" s="33"/>
+      <c r="I112" s="33"/>
+      <c r="J112" s="33"/>
+      <c r="K112" s="33"/>
+      <c r="L112" s="33"/>
+      <c r="M112" s="33"/>
     </row>
     <row r="113" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B113" s="32"/>
-      <c r="C113" s="32"/>
-      <c r="D113" s="32"/>
-      <c r="E113" s="32"/>
-      <c r="F113" s="32"/>
-      <c r="G113" s="32"/>
-      <c r="H113" s="32"/>
-      <c r="I113" s="32"/>
-      <c r="J113" s="32"/>
-      <c r="K113" s="32"/>
-      <c r="L113" s="32"/>
-      <c r="M113" s="32"/>
+      <c r="B113" s="33"/>
+      <c r="C113" s="33"/>
+      <c r="D113" s="33"/>
+      <c r="E113" s="33"/>
+      <c r="F113" s="33"/>
+      <c r="G113" s="33"/>
+      <c r="H113" s="33"/>
+      <c r="I113" s="33"/>
+      <c r="J113" s="33"/>
+      <c r="K113" s="33"/>
+      <c r="L113" s="33"/>
+      <c r="M113" s="33"/>
     </row>
     <row r="114" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B114" s="32"/>
-      <c r="C114" s="32"/>
-      <c r="D114" s="32"/>
-      <c r="E114" s="32"/>
-      <c r="F114" s="32"/>
-      <c r="G114" s="32"/>
-      <c r="H114" s="32"/>
-      <c r="I114" s="32"/>
-      <c r="J114" s="32"/>
-      <c r="K114" s="32"/>
-      <c r="L114" s="32"/>
-      <c r="M114" s="32"/>
+      <c r="B114" s="33"/>
+      <c r="C114" s="33"/>
+      <c r="D114" s="33"/>
+      <c r="E114" s="33"/>
+      <c r="F114" s="33"/>
+      <c r="G114" s="33"/>
+      <c r="H114" s="33"/>
+      <c r="I114" s="33"/>
+      <c r="J114" s="33"/>
+      <c r="K114" s="33"/>
+      <c r="L114" s="33"/>
+      <c r="M114" s="33"/>
     </row>
     <row r="115" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B115" s="32"/>
-      <c r="C115" s="32"/>
-      <c r="D115" s="32"/>
-      <c r="E115" s="32"/>
-      <c r="F115" s="32"/>
-      <c r="G115" s="32"/>
-      <c r="H115" s="32"/>
-      <c r="I115" s="32"/>
-      <c r="J115" s="32"/>
-      <c r="K115" s="32"/>
-      <c r="L115" s="32"/>
-      <c r="M115" s="32"/>
+      <c r="B115" s="33"/>
+      <c r="C115" s="33"/>
+      <c r="D115" s="33"/>
+      <c r="E115" s="33"/>
+      <c r="F115" s="33"/>
+      <c r="G115" s="33"/>
+      <c r="H115" s="33"/>
+      <c r="I115" s="33"/>
+      <c r="J115" s="33"/>
+      <c r="K115" s="33"/>
+      <c r="L115" s="33"/>
+      <c r="M115" s="33"/>
     </row>
     <row r="116" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B116" s="32"/>
-      <c r="C116" s="32"/>
-      <c r="D116" s="32"/>
-      <c r="E116" s="32"/>
-      <c r="F116" s="32"/>
-      <c r="G116" s="32"/>
-      <c r="H116" s="32"/>
-      <c r="I116" s="32"/>
-      <c r="J116" s="32"/>
-      <c r="K116" s="32"/>
-      <c r="L116" s="32"/>
-      <c r="M116" s="32"/>
+      <c r="B116" s="33"/>
+      <c r="C116" s="33"/>
+      <c r="D116" s="33"/>
+      <c r="E116" s="33"/>
+      <c r="F116" s="33"/>
+      <c r="G116" s="33"/>
+      <c r="H116" s="33"/>
+      <c r="I116" s="33"/>
+      <c r="J116" s="33"/>
+      <c r="K116" s="33"/>
+      <c r="L116" s="33"/>
+      <c r="M116" s="33"/>
     </row>
     <row r="117" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="32"/>
-      <c r="C117" s="32"/>
-      <c r="D117" s="32"/>
-      <c r="E117" s="32"/>
-      <c r="F117" s="32"/>
-      <c r="G117" s="32"/>
-      <c r="H117" s="32"/>
-      <c r="I117" s="32"/>
-      <c r="J117" s="32"/>
-      <c r="K117" s="32"/>
-      <c r="L117" s="32"/>
-      <c r="M117" s="32"/>
+      <c r="B117" s="33"/>
+      <c r="C117" s="33"/>
+      <c r="D117" s="33"/>
+      <c r="E117" s="33"/>
+      <c r="F117" s="33"/>
+      <c r="G117" s="33"/>
+      <c r="H117" s="33"/>
+      <c r="I117" s="33"/>
+      <c r="J117" s="33"/>
+      <c r="K117" s="33"/>
+      <c r="L117" s="33"/>
+      <c r="M117" s="33"/>
     </row>
     <row r="118" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B118" s="32"/>
-      <c r="C118" s="32"/>
-      <c r="D118" s="32"/>
-      <c r="E118" s="32"/>
-      <c r="F118" s="32"/>
-      <c r="G118" s="32"/>
-      <c r="H118" s="32"/>
-      <c r="I118" s="32"/>
-      <c r="J118" s="32"/>
-      <c r="K118" s="32"/>
-      <c r="L118" s="32"/>
-      <c r="M118" s="32"/>
+      <c r="B118" s="33"/>
+      <c r="C118" s="33"/>
+      <c r="D118" s="33"/>
+      <c r="E118" s="33"/>
+      <c r="F118" s="33"/>
+      <c r="G118" s="33"/>
+      <c r="H118" s="33"/>
+      <c r="I118" s="33"/>
+      <c r="J118" s="33"/>
+      <c r="K118" s="33"/>
+      <c r="L118" s="33"/>
+      <c r="M118" s="33"/>
     </row>
     <row r="119" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B119" s="32"/>
-      <c r="C119" s="32"/>
-      <c r="D119" s="32"/>
-      <c r="E119" s="32"/>
-      <c r="F119" s="32"/>
-      <c r="G119" s="32"/>
-      <c r="H119" s="32"/>
-      <c r="I119" s="32"/>
-      <c r="J119" s="32"/>
-      <c r="K119" s="32"/>
-      <c r="L119" s="32"/>
-      <c r="M119" s="32"/>
+      <c r="B119" s="33"/>
+      <c r="C119" s="33"/>
+      <c r="D119" s="33"/>
+      <c r="E119" s="33"/>
+      <c r="F119" s="33"/>
+      <c r="G119" s="33"/>
+      <c r="H119" s="33"/>
+      <c r="I119" s="33"/>
+      <c r="J119" s="33"/>
+      <c r="K119" s="33"/>
+      <c r="L119" s="33"/>
+      <c r="M119" s="33"/>
     </row>
     <row r="120" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B120" s="32"/>
-      <c r="C120" s="32"/>
-      <c r="D120" s="32"/>
-      <c r="E120" s="32"/>
-      <c r="F120" s="32"/>
-      <c r="G120" s="32"/>
-      <c r="H120" s="32"/>
-      <c r="I120" s="32"/>
-      <c r="J120" s="32"/>
-      <c r="K120" s="32"/>
-      <c r="L120" s="32"/>
-      <c r="M120" s="32"/>
+      <c r="B120" s="33"/>
+      <c r="C120" s="33"/>
+      <c r="D120" s="33"/>
+      <c r="E120" s="33"/>
+      <c r="F120" s="33"/>
+      <c r="G120" s="33"/>
+      <c r="H120" s="33"/>
+      <c r="I120" s="33"/>
+      <c r="J120" s="33"/>
+      <c r="K120" s="33"/>
+      <c r="L120" s="33"/>
+      <c r="M120" s="33"/>
     </row>
     <row r="121" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B121" s="32"/>
-      <c r="C121" s="32"/>
-      <c r="D121" s="32"/>
-      <c r="E121" s="32"/>
-      <c r="F121" s="32"/>
-      <c r="G121" s="32"/>
-      <c r="H121" s="32"/>
-      <c r="I121" s="32"/>
-      <c r="J121" s="32"/>
-      <c r="K121" s="32"/>
-      <c r="L121" s="32"/>
-      <c r="M121" s="32"/>
+      <c r="B121" s="33"/>
+      <c r="C121" s="33"/>
+      <c r="D121" s="33"/>
+      <c r="E121" s="33"/>
+      <c r="F121" s="33"/>
+      <c r="G121" s="33"/>
+      <c r="H121" s="33"/>
+      <c r="I121" s="33"/>
+      <c r="J121" s="33"/>
+      <c r="K121" s="33"/>
+      <c r="L121" s="33"/>
+      <c r="M121" s="33"/>
     </row>
     <row r="122" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B122" s="32"/>
-      <c r="C122" s="32"/>
-      <c r="D122" s="32"/>
-      <c r="E122" s="32"/>
-      <c r="F122" s="32"/>
-      <c r="G122" s="32"/>
-      <c r="H122" s="32"/>
-      <c r="I122" s="32"/>
-      <c r="J122" s="32"/>
-      <c r="K122" s="32"/>
-      <c r="L122" s="32"/>
-      <c r="M122" s="32"/>
+      <c r="B122" s="33"/>
+      <c r="C122" s="33"/>
+      <c r="D122" s="33"/>
+      <c r="E122" s="33"/>
+      <c r="F122" s="33"/>
+      <c r="G122" s="33"/>
+      <c r="H122" s="33"/>
+      <c r="I122" s="33"/>
+      <c r="J122" s="33"/>
+      <c r="K122" s="33"/>
+      <c r="L122" s="33"/>
+      <c r="M122" s="33"/>
     </row>
     <row r="123" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="32"/>
-      <c r="C123" s="32"/>
-      <c r="D123" s="32"/>
-      <c r="E123" s="32"/>
-      <c r="F123" s="32"/>
-      <c r="G123" s="32"/>
-      <c r="H123" s="32"/>
-      <c r="I123" s="32"/>
-      <c r="J123" s="32"/>
-      <c r="K123" s="32"/>
-      <c r="L123" s="32"/>
-      <c r="M123" s="32"/>
+      <c r="B123" s="33"/>
+      <c r="C123" s="33"/>
+      <c r="D123" s="33"/>
+      <c r="E123" s="33"/>
+      <c r="F123" s="33"/>
+      <c r="G123" s="33"/>
+      <c r="H123" s="33"/>
+      <c r="I123" s="33"/>
+      <c r="J123" s="33"/>
+      <c r="K123" s="33"/>
+      <c r="L123" s="33"/>
+      <c r="M123" s="33"/>
     </row>
     <row r="124" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B124" s="32"/>
-      <c r="C124" s="32"/>
-      <c r="D124" s="32"/>
-      <c r="E124" s="32"/>
-      <c r="F124" s="32"/>
-      <c r="G124" s="32"/>
-      <c r="H124" s="32"/>
-      <c r="I124" s="32"/>
-      <c r="J124" s="32"/>
-      <c r="K124" s="32"/>
-      <c r="L124" s="32"/>
-      <c r="M124" s="32"/>
+      <c r="B124" s="33"/>
+      <c r="C124" s="33"/>
+      <c r="D124" s="33"/>
+      <c r="E124" s="33"/>
+      <c r="F124" s="33"/>
+      <c r="G124" s="33"/>
+      <c r="H124" s="33"/>
+      <c r="I124" s="33"/>
+      <c r="J124" s="33"/>
+      <c r="K124" s="33"/>
+      <c r="L124" s="33"/>
+      <c r="M124" s="33"/>
     </row>
     <row r="125" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="32"/>
-      <c r="C125" s="32"/>
-      <c r="D125" s="32"/>
-      <c r="E125" s="32"/>
-      <c r="F125" s="32"/>
-      <c r="G125" s="32"/>
-      <c r="H125" s="32"/>
-      <c r="I125" s="32"/>
-      <c r="J125" s="32"/>
-      <c r="K125" s="32"/>
-      <c r="L125" s="32"/>
-      <c r="M125" s="32"/>
+      <c r="B125" s="33"/>
+      <c r="C125" s="33"/>
+      <c r="D125" s="33"/>
+      <c r="E125" s="33"/>
+      <c r="F125" s="33"/>
+      <c r="G125" s="33"/>
+      <c r="H125" s="33"/>
+      <c r="I125" s="33"/>
+      <c r="J125" s="33"/>
+      <c r="K125" s="33"/>
+      <c r="L125" s="33"/>
+      <c r="M125" s="33"/>
     </row>
     <row r="126" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B126" s="32"/>
-      <c r="C126" s="32"/>
-      <c r="D126" s="32"/>
-      <c r="E126" s="32"/>
-      <c r="F126" s="32"/>
-      <c r="G126" s="32"/>
-      <c r="H126" s="32"/>
-      <c r="I126" s="32"/>
-      <c r="J126" s="32"/>
-      <c r="K126" s="32"/>
-      <c r="L126" s="32"/>
-      <c r="M126" s="32"/>
+      <c r="B126" s="33"/>
+      <c r="C126" s="33"/>
+      <c r="D126" s="33"/>
+      <c r="E126" s="33"/>
+      <c r="F126" s="33"/>
+      <c r="G126" s="33"/>
+      <c r="H126" s="33"/>
+      <c r="I126" s="33"/>
+      <c r="J126" s="33"/>
+      <c r="K126" s="33"/>
+      <c r="L126" s="33"/>
+      <c r="M126" s="33"/>
     </row>
     <row r="127" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B127" s="32"/>
-      <c r="C127" s="32"/>
-      <c r="D127" s="32"/>
-      <c r="E127" s="32"/>
-      <c r="F127" s="32"/>
-      <c r="G127" s="32"/>
-      <c r="H127" s="32"/>
-      <c r="I127" s="32"/>
-      <c r="J127" s="32"/>
-      <c r="K127" s="32"/>
-      <c r="L127" s="32"/>
-      <c r="M127" s="32"/>
+      <c r="B127" s="33"/>
+      <c r="C127" s="33"/>
+      <c r="D127" s="33"/>
+      <c r="E127" s="33"/>
+      <c r="F127" s="33"/>
+      <c r="G127" s="33"/>
+      <c r="H127" s="33"/>
+      <c r="I127" s="33"/>
+      <c r="J127" s="33"/>
+      <c r="K127" s="33"/>
+      <c r="L127" s="33"/>
+      <c r="M127" s="33"/>
     </row>
     <row r="128" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B128" s="32"/>
-      <c r="C128" s="32"/>
-      <c r="D128" s="32"/>
-      <c r="E128" s="32"/>
-      <c r="F128" s="32"/>
-      <c r="G128" s="32"/>
-      <c r="H128" s="32"/>
-      <c r="I128" s="32"/>
-      <c r="J128" s="32"/>
-      <c r="K128" s="32"/>
-      <c r="L128" s="32"/>
-      <c r="M128" s="32"/>
+      <c r="B128" s="33"/>
+      <c r="C128" s="33"/>
+      <c r="D128" s="33"/>
+      <c r="E128" s="33"/>
+      <c r="F128" s="33"/>
+      <c r="G128" s="33"/>
+      <c r="H128" s="33"/>
+      <c r="I128" s="33"/>
+      <c r="J128" s="33"/>
+      <c r="K128" s="33"/>
+      <c r="L128" s="33"/>
+      <c r="M128" s="33"/>
     </row>
     <row r="129" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B129" s="32"/>
-      <c r="C129" s="32"/>
-      <c r="D129" s="32"/>
-      <c r="E129" s="32"/>
-      <c r="F129" s="32"/>
-      <c r="G129" s="32"/>
-      <c r="H129" s="32"/>
-      <c r="I129" s="32"/>
-      <c r="J129" s="32"/>
-      <c r="K129" s="32"/>
-      <c r="L129" s="32"/>
-      <c r="M129" s="32"/>
+      <c r="B129" s="33"/>
+      <c r="C129" s="33"/>
+      <c r="D129" s="33"/>
+      <c r="E129" s="33"/>
+      <c r="F129" s="33"/>
+      <c r="G129" s="33"/>
+      <c r="H129" s="33"/>
+      <c r="I129" s="33"/>
+      <c r="J129" s="33"/>
+      <c r="K129" s="33"/>
+      <c r="L129" s="33"/>
+      <c r="M129" s="33"/>
     </row>
     <row r="130" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B130" s="32"/>
-      <c r="C130" s="32"/>
-      <c r="D130" s="32"/>
-      <c r="E130" s="32"/>
-      <c r="F130" s="32"/>
-      <c r="G130" s="32"/>
-      <c r="H130" s="32"/>
-      <c r="I130" s="32"/>
-      <c r="J130" s="32"/>
-      <c r="K130" s="32"/>
-      <c r="L130" s="32"/>
-      <c r="M130" s="32"/>
+      <c r="B130" s="33"/>
+      <c r="C130" s="33"/>
+      <c r="D130" s="33"/>
+      <c r="E130" s="33"/>
+      <c r="F130" s="33"/>
+      <c r="G130" s="33"/>
+      <c r="H130" s="33"/>
+      <c r="I130" s="33"/>
+      <c r="J130" s="33"/>
+      <c r="K130" s="33"/>
+      <c r="L130" s="33"/>
+      <c r="M130" s="33"/>
     </row>
     <row r="131" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B131" s="32"/>
-      <c r="C131" s="32"/>
-      <c r="D131" s="32"/>
-      <c r="E131" s="32"/>
-      <c r="F131" s="32"/>
-      <c r="G131" s="32"/>
-      <c r="H131" s="32"/>
-      <c r="I131" s="32"/>
-      <c r="J131" s="32"/>
-      <c r="K131" s="32"/>
-      <c r="L131" s="32"/>
-      <c r="M131" s="32"/>
+      <c r="B131" s="33"/>
+      <c r="C131" s="33"/>
+      <c r="D131" s="33"/>
+      <c r="E131" s="33"/>
+      <c r="F131" s="33"/>
+      <c r="G131" s="33"/>
+      <c r="H131" s="33"/>
+      <c r="I131" s="33"/>
+      <c r="J131" s="33"/>
+      <c r="K131" s="33"/>
+      <c r="L131" s="33"/>
+      <c r="M131" s="33"/>
     </row>
     <row r="132" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B132" s="32"/>
-      <c r="C132" s="32"/>
-      <c r="D132" s="32"/>
-      <c r="E132" s="32"/>
-      <c r="F132" s="32"/>
-      <c r="G132" s="32"/>
-      <c r="H132" s="32"/>
-      <c r="I132" s="32"/>
-      <c r="J132" s="32"/>
-      <c r="K132" s="32"/>
-      <c r="L132" s="32"/>
-      <c r="M132" s="32"/>
+      <c r="B132" s="33"/>
+      <c r="C132" s="33"/>
+      <c r="D132" s="33"/>
+      <c r="E132" s="33"/>
+      <c r="F132" s="33"/>
+      <c r="G132" s="33"/>
+      <c r="H132" s="33"/>
+      <c r="I132" s="33"/>
+      <c r="J132" s="33"/>
+      <c r="K132" s="33"/>
+      <c r="L132" s="33"/>
+      <c r="M132" s="33"/>
     </row>
     <row r="133" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B133" s="32"/>
-      <c r="C133" s="32"/>
-      <c r="D133" s="32"/>
-      <c r="E133" s="32"/>
-      <c r="F133" s="32"/>
-      <c r="G133" s="32"/>
-      <c r="H133" s="32"/>
-      <c r="I133" s="32"/>
-      <c r="J133" s="32"/>
-      <c r="K133" s="32"/>
-      <c r="L133" s="32"/>
-      <c r="M133" s="32"/>
+      <c r="B133" s="33"/>
+      <c r="C133" s="33"/>
+      <c r="D133" s="33"/>
+      <c r="E133" s="33"/>
+      <c r="F133" s="33"/>
+      <c r="G133" s="33"/>
+      <c r="H133" s="33"/>
+      <c r="I133" s="33"/>
+      <c r="J133" s="33"/>
+      <c r="K133" s="33"/>
+      <c r="L133" s="33"/>
+      <c r="M133" s="33"/>
     </row>
     <row r="134" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B134" s="32"/>
-      <c r="C134" s="32"/>
-      <c r="D134" s="32"/>
-      <c r="E134" s="32"/>
-      <c r="F134" s="32"/>
-      <c r="G134" s="32"/>
-      <c r="H134" s="32"/>
-      <c r="I134" s="32"/>
-      <c r="J134" s="32"/>
-      <c r="K134" s="32"/>
-      <c r="L134" s="32"/>
-      <c r="M134" s="32"/>
+      <c r="B134" s="33"/>
+      <c r="C134" s="33"/>
+      <c r="D134" s="33"/>
+      <c r="E134" s="33"/>
+      <c r="F134" s="33"/>
+      <c r="G134" s="33"/>
+      <c r="H134" s="33"/>
+      <c r="I134" s="33"/>
+      <c r="J134" s="33"/>
+      <c r="K134" s="33"/>
+      <c r="L134" s="33"/>
+      <c r="M134" s="33"/>
     </row>
     <row r="135" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B135" s="32"/>
-      <c r="C135" s="32"/>
-      <c r="D135" s="32"/>
-      <c r="E135" s="32"/>
-      <c r="F135" s="32"/>
-      <c r="G135" s="32"/>
-      <c r="H135" s="32"/>
-      <c r="I135" s="32"/>
-      <c r="J135" s="32"/>
-      <c r="K135" s="32"/>
-      <c r="L135" s="32"/>
-      <c r="M135" s="32"/>
+      <c r="B135" s="33"/>
+      <c r="C135" s="33"/>
+      <c r="D135" s="33"/>
+      <c r="E135" s="33"/>
+      <c r="F135" s="33"/>
+      <c r="G135" s="33"/>
+      <c r="H135" s="33"/>
+      <c r="I135" s="33"/>
+      <c r="J135" s="33"/>
+      <c r="K135" s="33"/>
+      <c r="L135" s="33"/>
+      <c r="M135" s="33"/>
     </row>
     <row r="136" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B136" s="32"/>
-      <c r="C136" s="32"/>
-      <c r="D136" s="32"/>
-      <c r="E136" s="32"/>
-      <c r="F136" s="32"/>
-      <c r="G136" s="32"/>
-      <c r="H136" s="32"/>
-      <c r="I136" s="32"/>
-      <c r="J136" s="32"/>
-      <c r="K136" s="32"/>
-      <c r="L136" s="32"/>
-      <c r="M136" s="32"/>
+      <c r="B136" s="33"/>
+      <c r="C136" s="33"/>
+      <c r="D136" s="33"/>
+      <c r="E136" s="33"/>
+      <c r="F136" s="33"/>
+      <c r="G136" s="33"/>
+      <c r="H136" s="33"/>
+      <c r="I136" s="33"/>
+      <c r="J136" s="33"/>
+      <c r="K136" s="33"/>
+      <c r="L136" s="33"/>
+      <c r="M136" s="33"/>
     </row>
     <row r="137" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B137" s="32"/>
-      <c r="C137" s="32"/>
-      <c r="D137" s="32"/>
-      <c r="E137" s="32"/>
-      <c r="F137" s="32"/>
-      <c r="G137" s="32"/>
-      <c r="H137" s="32"/>
-      <c r="I137" s="32"/>
-      <c r="J137" s="32"/>
-      <c r="K137" s="32"/>
-      <c r="L137" s="32"/>
-      <c r="M137" s="32"/>
+      <c r="B137" s="33"/>
+      <c r="C137" s="33"/>
+      <c r="D137" s="33"/>
+      <c r="E137" s="33"/>
+      <c r="F137" s="33"/>
+      <c r="G137" s="33"/>
+      <c r="H137" s="33"/>
+      <c r="I137" s="33"/>
+      <c r="J137" s="33"/>
+      <c r="K137" s="33"/>
+      <c r="L137" s="33"/>
+      <c r="M137" s="33"/>
     </row>
     <row r="138" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B138" s="32"/>
-      <c r="C138" s="32"/>
-      <c r="D138" s="32"/>
-      <c r="E138" s="32"/>
-      <c r="F138" s="32"/>
-      <c r="G138" s="32"/>
-      <c r="H138" s="32"/>
-      <c r="I138" s="32"/>
-      <c r="J138" s="32"/>
-      <c r="K138" s="32"/>
-      <c r="L138" s="32"/>
-      <c r="M138" s="32"/>
+      <c r="B138" s="33"/>
+      <c r="C138" s="33"/>
+      <c r="D138" s="33"/>
+      <c r="E138" s="33"/>
+      <c r="F138" s="33"/>
+      <c r="G138" s="33"/>
+      <c r="H138" s="33"/>
+      <c r="I138" s="33"/>
+      <c r="J138" s="33"/>
+      <c r="K138" s="33"/>
+      <c r="L138" s="33"/>
+      <c r="M138" s="33"/>
     </row>
     <row r="139" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B139" s="32"/>
-      <c r="C139" s="32"/>
-      <c r="D139" s="32"/>
-      <c r="E139" s="32"/>
-      <c r="F139" s="32"/>
-      <c r="G139" s="32"/>
-      <c r="H139" s="32"/>
-      <c r="I139" s="32"/>
-      <c r="J139" s="32"/>
-      <c r="K139" s="32"/>
-      <c r="L139" s="32"/>
-      <c r="M139" s="32"/>
+      <c r="B139" s="33"/>
+      <c r="C139" s="33"/>
+      <c r="D139" s="33"/>
+      <c r="E139" s="33"/>
+      <c r="F139" s="33"/>
+      <c r="G139" s="33"/>
+      <c r="H139" s="33"/>
+      <c r="I139" s="33"/>
+      <c r="J139" s="33"/>
+      <c r="K139" s="33"/>
+      <c r="L139" s="33"/>
+      <c r="M139" s="33"/>
     </row>
     <row r="140" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B140" s="32"/>
-      <c r="C140" s="32"/>
-      <c r="D140" s="32"/>
-      <c r="E140" s="32"/>
-      <c r="F140" s="32"/>
-      <c r="G140" s="32"/>
-      <c r="H140" s="32"/>
-      <c r="I140" s="32"/>
-      <c r="J140" s="32"/>
-      <c r="K140" s="32"/>
-      <c r="L140" s="32"/>
-      <c r="M140" s="32"/>
+      <c r="B140" s="33"/>
+      <c r="C140" s="33"/>
+      <c r="D140" s="33"/>
+      <c r="E140" s="33"/>
+      <c r="F140" s="33"/>
+      <c r="G140" s="33"/>
+      <c r="H140" s="33"/>
+      <c r="I140" s="33"/>
+      <c r="J140" s="33"/>
+      <c r="K140" s="33"/>
+      <c r="L140" s="33"/>
+      <c r="M140" s="33"/>
     </row>
     <row r="141" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B141" s="32"/>
-      <c r="C141" s="32"/>
-      <c r="D141" s="32"/>
-      <c r="E141" s="32"/>
-      <c r="F141" s="32"/>
-      <c r="G141" s="32"/>
-      <c r="H141" s="32"/>
-      <c r="I141" s="32"/>
-      <c r="J141" s="32"/>
-      <c r="K141" s="32"/>
-      <c r="L141" s="32"/>
-      <c r="M141" s="32"/>
+      <c r="B141" s="33"/>
+      <c r="C141" s="33"/>
+      <c r="D141" s="33"/>
+      <c r="E141" s="33"/>
+      <c r="F141" s="33"/>
+      <c r="G141" s="33"/>
+      <c r="H141" s="33"/>
+      <c r="I141" s="33"/>
+      <c r="J141" s="33"/>
+      <c r="K141" s="33"/>
+      <c r="L141" s="33"/>
+      <c r="M141" s="33"/>
     </row>
     <row r="142" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B142" s="32"/>
-      <c r="C142" s="32"/>
-      <c r="D142" s="32"/>
-      <c r="E142" s="32"/>
-      <c r="F142" s="32"/>
-      <c r="G142" s="32"/>
-      <c r="H142" s="32"/>
-      <c r="I142" s="32"/>
-      <c r="J142" s="32"/>
-      <c r="K142" s="32"/>
-      <c r="L142" s="32"/>
-      <c r="M142" s="32"/>
+      <c r="B142" s="33"/>
+      <c r="C142" s="33"/>
+      <c r="D142" s="33"/>
+      <c r="E142" s="33"/>
+      <c r="F142" s="33"/>
+      <c r="G142" s="33"/>
+      <c r="H142" s="33"/>
+      <c r="I142" s="33"/>
+      <c r="J142" s="33"/>
+      <c r="K142" s="33"/>
+      <c r="L142" s="33"/>
+      <c r="M142" s="33"/>
     </row>
     <row r="143" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B143" s="32"/>
-      <c r="C143" s="32"/>
-      <c r="D143" s="32"/>
-      <c r="E143" s="32"/>
-      <c r="F143" s="32"/>
-      <c r="G143" s="32"/>
-      <c r="H143" s="32"/>
-      <c r="I143" s="32"/>
-      <c r="J143" s="32"/>
-      <c r="K143" s="32"/>
-      <c r="L143" s="32"/>
-      <c r="M143" s="32"/>
+      <c r="B143" s="33"/>
+      <c r="C143" s="33"/>
+      <c r="D143" s="33"/>
+      <c r="E143" s="33"/>
+      <c r="F143" s="33"/>
+      <c r="G143" s="33"/>
+      <c r="H143" s="33"/>
+      <c r="I143" s="33"/>
+      <c r="J143" s="33"/>
+      <c r="K143" s="33"/>
+      <c r="L143" s="33"/>
+      <c r="M143" s="33"/>
     </row>
     <row r="144" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B144" s="32"/>
-      <c r="C144" s="32"/>
-      <c r="D144" s="32"/>
-      <c r="E144" s="32"/>
-      <c r="F144" s="32"/>
-      <c r="G144" s="32"/>
-      <c r="H144" s="32"/>
-      <c r="I144" s="32"/>
-      <c r="J144" s="32"/>
-      <c r="K144" s="32"/>
-      <c r="L144" s="32"/>
-      <c r="M144" s="32"/>
+      <c r="B144" s="33"/>
+      <c r="C144" s="33"/>
+      <c r="D144" s="33"/>
+      <c r="E144" s="33"/>
+      <c r="F144" s="33"/>
+      <c r="G144" s="33"/>
+      <c r="H144" s="33"/>
+      <c r="I144" s="33"/>
+      <c r="J144" s="33"/>
+      <c r="K144" s="33"/>
+      <c r="L144" s="33"/>
+      <c r="M144" s="33"/>
     </row>
     <row r="145" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B145" s="32"/>
-      <c r="C145" s="32"/>
-      <c r="D145" s="32"/>
-      <c r="E145" s="32"/>
-      <c r="F145" s="32"/>
-      <c r="G145" s="32"/>
-      <c r="H145" s="32"/>
-      <c r="I145" s="32"/>
-      <c r="J145" s="32"/>
-      <c r="K145" s="32"/>
-      <c r="L145" s="32"/>
-      <c r="M145" s="32"/>
+      <c r="B145" s="33"/>
+      <c r="C145" s="33"/>
+      <c r="D145" s="33"/>
+      <c r="E145" s="33"/>
+      <c r="F145" s="33"/>
+      <c r="G145" s="33"/>
+      <c r="H145" s="33"/>
+      <c r="I145" s="33"/>
+      <c r="J145" s="33"/>
+      <c r="K145" s="33"/>
+      <c r="L145" s="33"/>
+      <c r="M145" s="33"/>
     </row>
     <row r="146" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B146" s="32"/>
-      <c r="C146" s="32"/>
-      <c r="D146" s="32"/>
-      <c r="E146" s="32"/>
-      <c r="F146" s="32"/>
-      <c r="G146" s="32"/>
-      <c r="H146" s="32"/>
-      <c r="I146" s="32"/>
-      <c r="J146" s="32"/>
-      <c r="K146" s="32"/>
-      <c r="L146" s="32"/>
-      <c r="M146" s="32"/>
+      <c r="B146" s="33"/>
+      <c r="C146" s="33"/>
+      <c r="D146" s="33"/>
+      <c r="E146" s="33"/>
+      <c r="F146" s="33"/>
+      <c r="G146" s="33"/>
+      <c r="H146" s="33"/>
+      <c r="I146" s="33"/>
+      <c r="J146" s="33"/>
+      <c r="K146" s="33"/>
+      <c r="L146" s="33"/>
+      <c r="M146" s="33"/>
     </row>
     <row r="147" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B147" s="32"/>
-      <c r="C147" s="32"/>
-      <c r="D147" s="32"/>
-      <c r="E147" s="32"/>
-      <c r="F147" s="32"/>
-      <c r="G147" s="32"/>
-      <c r="H147" s="32"/>
-      <c r="I147" s="32"/>
-      <c r="J147" s="32"/>
-      <c r="K147" s="32"/>
-      <c r="L147" s="32"/>
-      <c r="M147" s="32"/>
+      <c r="B147" s="33"/>
+      <c r="C147" s="33"/>
+      <c r="D147" s="33"/>
+      <c r="E147" s="33"/>
+      <c r="F147" s="33"/>
+      <c r="G147" s="33"/>
+      <c r="H147" s="33"/>
+      <c r="I147" s="33"/>
+      <c r="J147" s="33"/>
+      <c r="K147" s="33"/>
+      <c r="L147" s="33"/>
+      <c r="M147" s="33"/>
     </row>
     <row r="148" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B148" s="32"/>
-      <c r="C148" s="32"/>
-      <c r="D148" s="32"/>
-      <c r="E148" s="32"/>
-      <c r="F148" s="32"/>
-      <c r="G148" s="32"/>
-      <c r="H148" s="32"/>
-      <c r="I148" s="32"/>
-      <c r="J148" s="32"/>
-      <c r="K148" s="32"/>
-      <c r="L148" s="32"/>
-      <c r="M148" s="32"/>
+      <c r="B148" s="33"/>
+      <c r="C148" s="33"/>
+      <c r="D148" s="33"/>
+      <c r="E148" s="33"/>
+      <c r="F148" s="33"/>
+      <c r="G148" s="33"/>
+      <c r="H148" s="33"/>
+      <c r="I148" s="33"/>
+      <c r="J148" s="33"/>
+      <c r="K148" s="33"/>
+      <c r="L148" s="33"/>
+      <c r="M148" s="33"/>
     </row>
     <row r="149" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B149" s="32"/>
-      <c r="C149" s="32"/>
-      <c r="D149" s="32"/>
-      <c r="E149" s="32"/>
-      <c r="F149" s="32"/>
-      <c r="G149" s="32"/>
-      <c r="H149" s="32"/>
-      <c r="I149" s="32"/>
-      <c r="J149" s="32"/>
-      <c r="K149" s="32"/>
-      <c r="L149" s="32"/>
-      <c r="M149" s="32"/>
+      <c r="B149" s="33"/>
+      <c r="C149" s="33"/>
+      <c r="D149" s="33"/>
+      <c r="E149" s="33"/>
+      <c r="F149" s="33"/>
+      <c r="G149" s="33"/>
+      <c r="H149" s="33"/>
+      <c r="I149" s="33"/>
+      <c r="J149" s="33"/>
+      <c r="K149" s="33"/>
+      <c r="L149" s="33"/>
+      <c r="M149" s="33"/>
     </row>
     <row r="150" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B150" s="32"/>
-      <c r="C150" s="32"/>
-      <c r="D150" s="32"/>
-      <c r="E150" s="32"/>
-      <c r="F150" s="32"/>
-      <c r="G150" s="32"/>
-      <c r="H150" s="32"/>
-      <c r="I150" s="32"/>
-      <c r="J150" s="32"/>
-      <c r="K150" s="32"/>
-      <c r="L150" s="32"/>
-      <c r="M150" s="32"/>
+      <c r="B150" s="33"/>
+      <c r="C150" s="33"/>
+      <c r="D150" s="33"/>
+      <c r="E150" s="33"/>
+      <c r="F150" s="33"/>
+      <c r="G150" s="33"/>
+      <c r="H150" s="33"/>
+      <c r="I150" s="33"/>
+      <c r="J150" s="33"/>
+      <c r="K150" s="33"/>
+      <c r="L150" s="33"/>
+      <c r="M150" s="33"/>
     </row>
     <row r="151" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B151" s="32"/>
-      <c r="C151" s="32"/>
-      <c r="D151" s="32"/>
-      <c r="E151" s="32"/>
-      <c r="F151" s="32"/>
-      <c r="G151" s="32"/>
-      <c r="H151" s="32"/>
-      <c r="I151" s="32"/>
-      <c r="J151" s="32"/>
-      <c r="K151" s="32"/>
-      <c r="L151" s="32"/>
-      <c r="M151" s="32"/>
+      <c r="B151" s="33"/>
+      <c r="C151" s="33"/>
+      <c r="D151" s="33"/>
+      <c r="E151" s="33"/>
+      <c r="F151" s="33"/>
+      <c r="G151" s="33"/>
+      <c r="H151" s="33"/>
+      <c r="I151" s="33"/>
+      <c r="J151" s="33"/>
+      <c r="K151" s="33"/>
+      <c r="L151" s="33"/>
+      <c r="M151" s="33"/>
     </row>
     <row r="152" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B152" s="32"/>
-      <c r="C152" s="32"/>
-      <c r="D152" s="32"/>
-      <c r="E152" s="32"/>
-      <c r="F152" s="32"/>
-      <c r="G152" s="32"/>
-      <c r="H152" s="32"/>
-      <c r="I152" s="32"/>
-      <c r="J152" s="32"/>
-      <c r="K152" s="32"/>
-      <c r="L152" s="32"/>
-      <c r="M152" s="32"/>
+      <c r="B152" s="33"/>
+      <c r="C152" s="33"/>
+      <c r="D152" s="33"/>
+      <c r="E152" s="33"/>
+      <c r="F152" s="33"/>
+      <c r="G152" s="33"/>
+      <c r="H152" s="33"/>
+      <c r="I152" s="33"/>
+      <c r="J152" s="33"/>
+      <c r="K152" s="33"/>
+      <c r="L152" s="33"/>
+      <c r="M152" s="33"/>
     </row>
     <row r="153" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B153" s="32"/>
-      <c r="C153" s="32"/>
-      <c r="D153" s="32"/>
-      <c r="E153" s="32"/>
-      <c r="F153" s="32"/>
-      <c r="G153" s="32"/>
-      <c r="H153" s="32"/>
-      <c r="I153" s="32"/>
-      <c r="J153" s="32"/>
-      <c r="K153" s="32"/>
-      <c r="L153" s="32"/>
-      <c r="M153" s="32"/>
+      <c r="B153" s="33"/>
+      <c r="C153" s="33"/>
+      <c r="D153" s="33"/>
+      <c r="E153" s="33"/>
+      <c r="F153" s="33"/>
+      <c r="G153" s="33"/>
+      <c r="H153" s="33"/>
+      <c r="I153" s="33"/>
+      <c r="J153" s="33"/>
+      <c r="K153" s="33"/>
+      <c r="L153" s="33"/>
+      <c r="M153" s="33"/>
     </row>
     <row r="154" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B154" s="32"/>
-      <c r="C154" s="32"/>
-      <c r="D154" s="32"/>
-      <c r="E154" s="32"/>
-      <c r="F154" s="32"/>
-      <c r="G154" s="32"/>
-      <c r="H154" s="32"/>
-      <c r="I154" s="32"/>
-      <c r="J154" s="32"/>
-      <c r="K154" s="32"/>
-      <c r="L154" s="32"/>
-      <c r="M154" s="32"/>
+      <c r="B154" s="33"/>
+      <c r="C154" s="33"/>
+      <c r="D154" s="33"/>
+      <c r="E154" s="33"/>
+      <c r="F154" s="33"/>
+      <c r="G154" s="33"/>
+      <c r="H154" s="33"/>
+      <c r="I154" s="33"/>
+      <c r="J154" s="33"/>
+      <c r="K154" s="33"/>
+      <c r="L154" s="33"/>
+      <c r="M154" s="33"/>
     </row>
     <row r="155" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B155" s="32"/>
-      <c r="C155" s="32"/>
-      <c r="D155" s="32"/>
-      <c r="E155" s="32"/>
-      <c r="F155" s="32"/>
-      <c r="G155" s="32"/>
-      <c r="H155" s="32"/>
-      <c r="I155" s="32"/>
-      <c r="J155" s="32"/>
-      <c r="K155" s="32"/>
-      <c r="L155" s="32"/>
-      <c r="M155" s="32"/>
+      <c r="B155" s="33"/>
+      <c r="C155" s="33"/>
+      <c r="D155" s="33"/>
+      <c r="E155" s="33"/>
+      <c r="F155" s="33"/>
+      <c r="G155" s="33"/>
+      <c r="H155" s="33"/>
+      <c r="I155" s="33"/>
+      <c r="J155" s="33"/>
+      <c r="K155" s="33"/>
+      <c r="L155" s="33"/>
+      <c r="M155" s="33"/>
     </row>
     <row r="156" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B156" s="32"/>
-      <c r="C156" s="32"/>
-      <c r="D156" s="32"/>
-      <c r="E156" s="32"/>
-      <c r="F156" s="32"/>
-      <c r="G156" s="32"/>
-      <c r="H156" s="32"/>
-      <c r="I156" s="32"/>
-      <c r="J156" s="32"/>
-      <c r="K156" s="32"/>
-      <c r="L156" s="32"/>
-      <c r="M156" s="32"/>
+      <c r="B156" s="33"/>
+      <c r="C156" s="33"/>
+      <c r="D156" s="33"/>
+      <c r="E156" s="33"/>
+      <c r="F156" s="33"/>
+      <c r="G156" s="33"/>
+      <c r="H156" s="33"/>
+      <c r="I156" s="33"/>
+      <c r="J156" s="33"/>
+      <c r="K156" s="33"/>
+      <c r="L156" s="33"/>
+      <c r="M156" s="33"/>
     </row>
     <row r="157" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B157" s="32"/>
-      <c r="C157" s="32"/>
-      <c r="D157" s="32"/>
-      <c r="E157" s="32"/>
-      <c r="F157" s="32"/>
-      <c r="G157" s="32"/>
-      <c r="H157" s="32"/>
-      <c r="I157" s="32"/>
-      <c r="J157" s="32"/>
-      <c r="K157" s="32"/>
-      <c r="L157" s="32"/>
-      <c r="M157" s="32"/>
+      <c r="B157" s="33"/>
+      <c r="C157" s="33"/>
+      <c r="D157" s="33"/>
+      <c r="E157" s="33"/>
+      <c r="F157" s="33"/>
+      <c r="G157" s="33"/>
+      <c r="H157" s="33"/>
+      <c r="I157" s="33"/>
+      <c r="J157" s="33"/>
+      <c r="K157" s="33"/>
+      <c r="L157" s="33"/>
+      <c r="M157" s="33"/>
     </row>
     <row r="158" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B158" s="32"/>
-      <c r="C158" s="32"/>
-      <c r="D158" s="32"/>
-      <c r="E158" s="32"/>
-      <c r="F158" s="32"/>
-      <c r="G158" s="32"/>
-      <c r="H158" s="32"/>
-      <c r="I158" s="32"/>
-      <c r="J158" s="32"/>
-      <c r="K158" s="32"/>
-      <c r="L158" s="32"/>
-      <c r="M158" s="32"/>
+      <c r="B158" s="33"/>
+      <c r="C158" s="33"/>
+      <c r="D158" s="33"/>
+      <c r="E158" s="33"/>
+      <c r="F158" s="33"/>
+      <c r="G158" s="33"/>
+      <c r="H158" s="33"/>
+      <c r="I158" s="33"/>
+      <c r="J158" s="33"/>
+      <c r="K158" s="33"/>
+      <c r="L158" s="33"/>
+      <c r="M158" s="33"/>
     </row>
     <row r="159" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B159" s="32"/>
-      <c r="C159" s="32"/>
-      <c r="D159" s="32"/>
-      <c r="E159" s="32"/>
-      <c r="F159" s="32"/>
-      <c r="G159" s="32"/>
-      <c r="H159" s="32"/>
-      <c r="I159" s="32"/>
-      <c r="J159" s="32"/>
-      <c r="K159" s="32"/>
-      <c r="L159" s="32"/>
-      <c r="M159" s="32"/>
+      <c r="B159" s="33"/>
+      <c r="C159" s="33"/>
+      <c r="D159" s="33"/>
+      <c r="E159" s="33"/>
+      <c r="F159" s="33"/>
+      <c r="G159" s="33"/>
+      <c r="H159" s="33"/>
+      <c r="I159" s="33"/>
+      <c r="J159" s="33"/>
+      <c r="K159" s="33"/>
+      <c r="L159" s="33"/>
+      <c r="M159" s="33"/>
     </row>
     <row r="160" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B160" s="32"/>
-      <c r="C160" s="32"/>
-      <c r="D160" s="32"/>
-      <c r="E160" s="32"/>
-      <c r="F160" s="32"/>
-      <c r="G160" s="32"/>
-      <c r="H160" s="32"/>
-      <c r="I160" s="32"/>
-      <c r="J160" s="32"/>
-      <c r="K160" s="32"/>
-      <c r="L160" s="32"/>
-      <c r="M160" s="32"/>
+      <c r="B160" s="33"/>
+      <c r="C160" s="33"/>
+      <c r="D160" s="33"/>
+      <c r="E160" s="33"/>
+      <c r="F160" s="33"/>
+      <c r="G160" s="33"/>
+      <c r="H160" s="33"/>
+      <c r="I160" s="33"/>
+      <c r="J160" s="33"/>
+      <c r="K160" s="33"/>
+      <c r="L160" s="33"/>
+      <c r="M160" s="33"/>
     </row>
     <row r="161" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B161" s="32"/>
-      <c r="C161" s="32"/>
-      <c r="D161" s="32"/>
-      <c r="E161" s="32"/>
-      <c r="F161" s="32"/>
-      <c r="G161" s="32"/>
-      <c r="H161" s="32"/>
-      <c r="I161" s="32"/>
-      <c r="J161" s="32"/>
-      <c r="K161" s="32"/>
-      <c r="L161" s="32"/>
-      <c r="M161" s="32"/>
+      <c r="B161" s="33"/>
+      <c r="C161" s="33"/>
+      <c r="D161" s="33"/>
+      <c r="E161" s="33"/>
+      <c r="F161" s="33"/>
+      <c r="G161" s="33"/>
+      <c r="H161" s="33"/>
+      <c r="I161" s="33"/>
+      <c r="J161" s="33"/>
+      <c r="K161" s="33"/>
+      <c r="L161" s="33"/>
+      <c r="M161" s="33"/>
     </row>
     <row r="162" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B162" s="32"/>
-      <c r="C162" s="32"/>
-      <c r="D162" s="32"/>
-      <c r="E162" s="32"/>
-      <c r="F162" s="32"/>
-      <c r="G162" s="32"/>
-      <c r="H162" s="32"/>
-      <c r="I162" s="32"/>
-      <c r="J162" s="32"/>
-      <c r="K162" s="32"/>
-      <c r="L162" s="32"/>
-      <c r="M162" s="32"/>
+      <c r="B162" s="33"/>
+      <c r="C162" s="33"/>
+      <c r="D162" s="33"/>
+      <c r="E162" s="33"/>
+      <c r="F162" s="33"/>
+      <c r="G162" s="33"/>
+      <c r="H162" s="33"/>
+      <c r="I162" s="33"/>
+      <c r="J162" s="33"/>
+      <c r="K162" s="33"/>
+      <c r="L162" s="33"/>
+      <c r="M162" s="33"/>
     </row>
     <row r="163" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B163" s="32"/>
-      <c r="C163" s="32"/>
-      <c r="D163" s="32"/>
-      <c r="E163" s="32"/>
-      <c r="F163" s="32"/>
-      <c r="G163" s="32"/>
-      <c r="H163" s="32"/>
-      <c r="I163" s="32"/>
-      <c r="J163" s="32"/>
-      <c r="K163" s="32"/>
-      <c r="L163" s="32"/>
-      <c r="M163" s="32"/>
+      <c r="B163" s="33"/>
+      <c r="C163" s="33"/>
+      <c r="D163" s="33"/>
+      <c r="E163" s="33"/>
+      <c r="F163" s="33"/>
+      <c r="G163" s="33"/>
+      <c r="H163" s="33"/>
+      <c r="I163" s="33"/>
+      <c r="J163" s="33"/>
+      <c r="K163" s="33"/>
+      <c r="L163" s="33"/>
+      <c r="M163" s="33"/>
     </row>
     <row r="164" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B164" s="32"/>
-      <c r="C164" s="32"/>
-      <c r="D164" s="32"/>
-      <c r="E164" s="32"/>
-      <c r="F164" s="32"/>
-      <c r="G164" s="32"/>
-      <c r="H164" s="32"/>
-      <c r="I164" s="32"/>
-      <c r="J164" s="32"/>
-      <c r="K164" s="32"/>
-      <c r="L164" s="32"/>
-      <c r="M164" s="32"/>
+      <c r="B164" s="33"/>
+      <c r="C164" s="33"/>
+      <c r="D164" s="33"/>
+      <c r="E164" s="33"/>
+      <c r="F164" s="33"/>
+      <c r="G164" s="33"/>
+      <c r="H164" s="33"/>
+      <c r="I164" s="33"/>
+      <c r="J164" s="33"/>
+      <c r="K164" s="33"/>
+      <c r="L164" s="33"/>
+      <c r="M164" s="33"/>
     </row>
     <row r="165" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B165" s="32"/>
-      <c r="C165" s="32"/>
-      <c r="D165" s="32"/>
-      <c r="E165" s="32"/>
-      <c r="F165" s="32"/>
-      <c r="G165" s="32"/>
-      <c r="H165" s="32"/>
-      <c r="I165" s="32"/>
-      <c r="J165" s="32"/>
-      <c r="K165" s="32"/>
-      <c r="L165" s="32"/>
-      <c r="M165" s="32"/>
+      <c r="B165" s="33"/>
+      <c r="C165" s="33"/>
+      <c r="D165" s="33"/>
+      <c r="E165" s="33"/>
+      <c r="F165" s="33"/>
+      <c r="G165" s="33"/>
+      <c r="H165" s="33"/>
+      <c r="I165" s="33"/>
+      <c r="J165" s="33"/>
+      <c r="K165" s="33"/>
+      <c r="L165" s="33"/>
+      <c r="M165" s="33"/>
     </row>
     <row r="166" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B166" s="32"/>
-      <c r="C166" s="32"/>
-      <c r="D166" s="32"/>
-      <c r="E166" s="32"/>
-      <c r="F166" s="32"/>
-      <c r="G166" s="32"/>
-      <c r="H166" s="32"/>
-      <c r="I166" s="32"/>
-      <c r="J166" s="32"/>
-      <c r="K166" s="32"/>
-      <c r="L166" s="32"/>
-      <c r="M166" s="32"/>
+      <c r="B166" s="33"/>
+      <c r="C166" s="33"/>
+      <c r="D166" s="33"/>
+      <c r="E166" s="33"/>
+      <c r="F166" s="33"/>
+      <c r="G166" s="33"/>
+      <c r="H166" s="33"/>
+      <c r="I166" s="33"/>
+      <c r="J166" s="33"/>
+      <c r="K166" s="33"/>
+      <c r="L166" s="33"/>
+      <c r="M166" s="33"/>
     </row>
     <row r="167" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B167" s="32"/>
-      <c r="C167" s="32"/>
-      <c r="D167" s="32"/>
-      <c r="E167" s="32"/>
-      <c r="F167" s="32"/>
-      <c r="G167" s="32"/>
-      <c r="H167" s="32"/>
-      <c r="I167" s="32"/>
-      <c r="J167" s="32"/>
-      <c r="K167" s="32"/>
-      <c r="L167" s="32"/>
-      <c r="M167" s="32"/>
+      <c r="B167" s="33"/>
+      <c r="C167" s="33"/>
+      <c r="D167" s="33"/>
+      <c r="E167" s="33"/>
+      <c r="F167" s="33"/>
+      <c r="G167" s="33"/>
+      <c r="H167" s="33"/>
+      <c r="I167" s="33"/>
+      <c r="J167" s="33"/>
+      <c r="K167" s="33"/>
+      <c r="L167" s="33"/>
+      <c r="M167" s="33"/>
     </row>
     <row r="168" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B168" s="32"/>
-      <c r="C168" s="32"/>
-      <c r="D168" s="32"/>
-      <c r="E168" s="32"/>
-      <c r="F168" s="32"/>
-      <c r="G168" s="32"/>
-      <c r="H168" s="32"/>
-      <c r="I168" s="32"/>
-      <c r="J168" s="32"/>
-      <c r="K168" s="32"/>
-      <c r="L168" s="32"/>
-      <c r="M168" s="32"/>
+      <c r="B168" s="33"/>
+      <c r="C168" s="33"/>
+      <c r="D168" s="33"/>
+      <c r="E168" s="33"/>
+      <c r="F168" s="33"/>
+      <c r="G168" s="33"/>
+      <c r="H168" s="33"/>
+      <c r="I168" s="33"/>
+      <c r="J168" s="33"/>
+      <c r="K168" s="33"/>
+      <c r="L168" s="33"/>
+      <c r="M168" s="33"/>
     </row>
     <row r="169" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B169" s="32"/>
-      <c r="C169" s="32"/>
-      <c r="D169" s="32"/>
-      <c r="E169" s="32"/>
-      <c r="F169" s="32"/>
-      <c r="G169" s="32"/>
-      <c r="H169" s="32"/>
-      <c r="I169" s="32"/>
-      <c r="J169" s="32"/>
-      <c r="K169" s="32"/>
-      <c r="L169" s="32"/>
-      <c r="M169" s="32"/>
+      <c r="B169" s="33"/>
+      <c r="C169" s="33"/>
+      <c r="D169" s="33"/>
+      <c r="E169" s="33"/>
+      <c r="F169" s="33"/>
+      <c r="G169" s="33"/>
+      <c r="H169" s="33"/>
+      <c r="I169" s="33"/>
+      <c r="J169" s="33"/>
+      <c r="K169" s="33"/>
+      <c r="L169" s="33"/>
+      <c r="M169" s="33"/>
     </row>
     <row r="170" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B170" s="32"/>
-      <c r="C170" s="32"/>
-      <c r="D170" s="32"/>
-      <c r="E170" s="32"/>
-      <c r="F170" s="32"/>
-      <c r="G170" s="32"/>
-      <c r="H170" s="32"/>
-      <c r="I170" s="32"/>
-      <c r="J170" s="32"/>
-      <c r="K170" s="32"/>
-      <c r="L170" s="32"/>
-      <c r="M170" s="32"/>
+      <c r="B170" s="33"/>
+      <c r="C170" s="33"/>
+      <c r="D170" s="33"/>
+      <c r="E170" s="33"/>
+      <c r="F170" s="33"/>
+      <c r="G170" s="33"/>
+      <c r="H170" s="33"/>
+      <c r="I170" s="33"/>
+      <c r="J170" s="33"/>
+      <c r="K170" s="33"/>
+      <c r="L170" s="33"/>
+      <c r="M170" s="33"/>
     </row>
     <row r="171" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B171" s="32"/>
-      <c r="C171" s="32"/>
-      <c r="D171" s="32"/>
-      <c r="E171" s="32"/>
-      <c r="F171" s="32"/>
-      <c r="G171" s="32"/>
-      <c r="H171" s="32"/>
-      <c r="I171" s="32"/>
-      <c r="J171" s="32"/>
-      <c r="K171" s="32"/>
-      <c r="L171" s="32"/>
-      <c r="M171" s="32"/>
+      <c r="B171" s="33"/>
+      <c r="C171" s="33"/>
+      <c r="D171" s="33"/>
+      <c r="E171" s="33"/>
+      <c r="F171" s="33"/>
+      <c r="G171" s="33"/>
+      <c r="H171" s="33"/>
+      <c r="I171" s="33"/>
+      <c r="J171" s="33"/>
+      <c r="K171" s="33"/>
+      <c r="L171" s="33"/>
+      <c r="M171" s="33"/>
     </row>
     <row r="172" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B172" s="32"/>
-      <c r="C172" s="32"/>
-      <c r="D172" s="32"/>
-      <c r="E172" s="32"/>
-      <c r="F172" s="32"/>
-      <c r="G172" s="32"/>
-      <c r="H172" s="32"/>
-      <c r="I172" s="32"/>
-      <c r="J172" s="32"/>
-      <c r="K172" s="32"/>
-      <c r="L172" s="32"/>
-      <c r="M172" s="32"/>
+      <c r="B172" s="33"/>
+      <c r="C172" s="33"/>
+      <c r="D172" s="33"/>
+      <c r="E172" s="33"/>
+      <c r="F172" s="33"/>
+      <c r="G172" s="33"/>
+      <c r="H172" s="33"/>
+      <c r="I172" s="33"/>
+      <c r="J172" s="33"/>
+      <c r="K172" s="33"/>
+      <c r="L172" s="33"/>
+      <c r="M172" s="33"/>
     </row>
     <row r="173" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B173" s="32"/>
-      <c r="C173" s="32"/>
-      <c r="D173" s="32"/>
-      <c r="E173" s="32"/>
-      <c r="F173" s="32"/>
-      <c r="G173" s="32"/>
-      <c r="H173" s="32"/>
-      <c r="I173" s="32"/>
-      <c r="J173" s="32"/>
-      <c r="K173" s="32"/>
-      <c r="L173" s="32"/>
-      <c r="M173" s="32"/>
+      <c r="B173" s="33"/>
+      <c r="C173" s="33"/>
+      <c r="D173" s="33"/>
+      <c r="E173" s="33"/>
+      <c r="F173" s="33"/>
+      <c r="G173" s="33"/>
+      <c r="H173" s="33"/>
+      <c r="I173" s="33"/>
+      <c r="J173" s="33"/>
+      <c r="K173" s="33"/>
+      <c r="L173" s="33"/>
+      <c r="M173" s="33"/>
     </row>
     <row r="174" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B174" s="32"/>
-      <c r="C174" s="32"/>
-      <c r="D174" s="32"/>
-      <c r="E174" s="32"/>
-      <c r="F174" s="32"/>
-      <c r="G174" s="32"/>
-      <c r="H174" s="32"/>
-      <c r="I174" s="32"/>
-      <c r="J174" s="32"/>
-      <c r="K174" s="32"/>
-      <c r="L174" s="32"/>
-      <c r="M174" s="32"/>
+      <c r="B174" s="33"/>
+      <c r="C174" s="33"/>
+      <c r="D174" s="33"/>
+      <c r="E174" s="33"/>
+      <c r="F174" s="33"/>
+      <c r="G174" s="33"/>
+      <c r="H174" s="33"/>
+      <c r="I174" s="33"/>
+      <c r="J174" s="33"/>
+      <c r="K174" s="33"/>
+      <c r="L174" s="33"/>
+      <c r="M174" s="33"/>
     </row>
     <row r="175" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B175" s="32"/>
-      <c r="C175" s="32"/>
-      <c r="D175" s="32"/>
-      <c r="E175" s="32"/>
-      <c r="F175" s="32"/>
-      <c r="G175" s="32"/>
-      <c r="H175" s="32"/>
-      <c r="I175" s="32"/>
-      <c r="J175" s="32"/>
-      <c r="K175" s="32"/>
-      <c r="L175" s="32"/>
-      <c r="M175" s="32"/>
+      <c r="B175" s="33"/>
+      <c r="C175" s="33"/>
+      <c r="D175" s="33"/>
+      <c r="E175" s="33"/>
+      <c r="F175" s="33"/>
+      <c r="G175" s="33"/>
+      <c r="H175" s="33"/>
+      <c r="I175" s="33"/>
+      <c r="J175" s="33"/>
+      <c r="K175" s="33"/>
+      <c r="L175" s="33"/>
+      <c r="M175" s="33"/>
     </row>
     <row r="176" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B176" s="32"/>
-      <c r="C176" s="32"/>
-      <c r="D176" s="32"/>
-      <c r="E176" s="32"/>
-      <c r="F176" s="32"/>
-      <c r="G176" s="32"/>
-      <c r="H176" s="32"/>
-      <c r="I176" s="32"/>
-      <c r="J176" s="32"/>
-      <c r="K176" s="32"/>
-      <c r="L176" s="32"/>
-      <c r="M176" s="32"/>
+      <c r="B176" s="33"/>
+      <c r="C176" s="33"/>
+      <c r="D176" s="33"/>
+      <c r="E176" s="33"/>
+      <c r="F176" s="33"/>
+      <c r="G176" s="33"/>
+      <c r="H176" s="33"/>
+      <c r="I176" s="33"/>
+      <c r="J176" s="33"/>
+      <c r="K176" s="33"/>
+      <c r="L176" s="33"/>
+      <c r="M176" s="33"/>
     </row>
     <row r="177" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B177" s="32"/>
-      <c r="C177" s="32"/>
-      <c r="D177" s="32"/>
-      <c r="E177" s="32"/>
-      <c r="F177" s="32"/>
-      <c r="G177" s="32"/>
-      <c r="H177" s="32"/>
-      <c r="I177" s="32"/>
-      <c r="J177" s="32"/>
-      <c r="K177" s="32"/>
-      <c r="L177" s="32"/>
-      <c r="M177" s="32"/>
+      <c r="B177" s="33"/>
+      <c r="C177" s="33"/>
+      <c r="D177" s="33"/>
+      <c r="E177" s="33"/>
+      <c r="F177" s="33"/>
+      <c r="G177" s="33"/>
+      <c r="H177" s="33"/>
+      <c r="I177" s="33"/>
+      <c r="J177" s="33"/>
+      <c r="K177" s="33"/>
+      <c r="L177" s="33"/>
+      <c r="M177" s="33"/>
     </row>
     <row r="178" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B178" s="32"/>
-      <c r="C178" s="32"/>
-      <c r="D178" s="32"/>
-      <c r="E178" s="32"/>
-      <c r="F178" s="32"/>
-      <c r="G178" s="32"/>
-      <c r="H178" s="32"/>
-      <c r="I178" s="32"/>
-      <c r="J178" s="32"/>
-      <c r="K178" s="32"/>
-      <c r="L178" s="32"/>
-      <c r="M178" s="32"/>
+      <c r="B178" s="33"/>
+      <c r="C178" s="33"/>
+      <c r="D178" s="33"/>
+      <c r="E178" s="33"/>
+      <c r="F178" s="33"/>
+      <c r="G178" s="33"/>
+      <c r="H178" s="33"/>
+      <c r="I178" s="33"/>
+      <c r="J178" s="33"/>
+      <c r="K178" s="33"/>
+      <c r="L178" s="33"/>
+      <c r="M178" s="33"/>
     </row>
     <row r="179" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B179" s="32"/>
-      <c r="C179" s="32"/>
-      <c r="D179" s="32"/>
-      <c r="E179" s="32"/>
-      <c r="F179" s="32"/>
-      <c r="G179" s="32"/>
-      <c r="H179" s="32"/>
-      <c r="I179" s="32"/>
-      <c r="J179" s="32"/>
-      <c r="K179" s="32"/>
-      <c r="L179" s="32"/>
-      <c r="M179" s="32"/>
+      <c r="B179" s="33"/>
+      <c r="C179" s="33"/>
+      <c r="D179" s="33"/>
+      <c r="E179" s="33"/>
+      <c r="F179" s="33"/>
+      <c r="G179" s="33"/>
+      <c r="H179" s="33"/>
+      <c r="I179" s="33"/>
+      <c r="J179" s="33"/>
+      <c r="K179" s="33"/>
+      <c r="L179" s="33"/>
+      <c r="M179" s="33"/>
     </row>
     <row r="180" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B180" s="32"/>
-      <c r="C180" s="32"/>
-      <c r="D180" s="32"/>
-      <c r="E180" s="32"/>
-      <c r="F180" s="32"/>
-      <c r="G180" s="32"/>
-      <c r="H180" s="32"/>
-      <c r="I180" s="32"/>
-      <c r="J180" s="32"/>
-      <c r="K180" s="32"/>
-      <c r="L180" s="32"/>
-      <c r="M180" s="32"/>
+      <c r="B180" s="33"/>
+      <c r="C180" s="33"/>
+      <c r="D180" s="33"/>
+      <c r="E180" s="33"/>
+      <c r="F180" s="33"/>
+      <c r="G180" s="33"/>
+      <c r="H180" s="33"/>
+      <c r="I180" s="33"/>
+      <c r="J180" s="33"/>
+      <c r="K180" s="33"/>
+      <c r="L180" s="33"/>
+      <c r="M180" s="33"/>
     </row>
     <row r="181" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B181" s="32"/>
-      <c r="C181" s="32"/>
-      <c r="D181" s="32"/>
-      <c r="E181" s="32"/>
-      <c r="F181" s="32"/>
-      <c r="G181" s="32"/>
-      <c r="H181" s="32"/>
-      <c r="I181" s="32"/>
-      <c r="J181" s="32"/>
-      <c r="K181" s="32"/>
-      <c r="L181" s="32"/>
-      <c r="M181" s="32"/>
+      <c r="B181" s="33"/>
+      <c r="C181" s="33"/>
+      <c r="D181" s="33"/>
+      <c r="E181" s="33"/>
+      <c r="F181" s="33"/>
+      <c r="G181" s="33"/>
+      <c r="H181" s="33"/>
+      <c r="I181" s="33"/>
+      <c r="J181" s="33"/>
+      <c r="K181" s="33"/>
+      <c r="L181" s="33"/>
+      <c r="M181" s="33"/>
     </row>
     <row r="182" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B182" s="32"/>
-      <c r="C182" s="32"/>
-      <c r="D182" s="32"/>
-      <c r="E182" s="32"/>
-      <c r="F182" s="32"/>
-      <c r="G182" s="32"/>
-      <c r="H182" s="32"/>
-      <c r="I182" s="32"/>
-      <c r="J182" s="32"/>
-      <c r="K182" s="32"/>
-      <c r="L182" s="32"/>
-      <c r="M182" s="32"/>
+      <c r="B182" s="33"/>
+      <c r="C182" s="33"/>
+      <c r="D182" s="33"/>
+      <c r="E182" s="33"/>
+      <c r="F182" s="33"/>
+      <c r="G182" s="33"/>
+      <c r="H182" s="33"/>
+      <c r="I182" s="33"/>
+      <c r="J182" s="33"/>
+      <c r="K182" s="33"/>
+      <c r="L182" s="33"/>
+      <c r="M182" s="33"/>
     </row>
     <row r="183" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B183" s="32"/>
-      <c r="C183" s="32"/>
-      <c r="D183" s="32"/>
-      <c r="E183" s="32"/>
-      <c r="F183" s="32"/>
-      <c r="G183" s="32"/>
-      <c r="H183" s="32"/>
-      <c r="I183" s="32"/>
-      <c r="J183" s="32"/>
-      <c r="K183" s="32"/>
-      <c r="L183" s="32"/>
-      <c r="M183" s="32"/>
+      <c r="B183" s="33"/>
+      <c r="C183" s="33"/>
+      <c r="D183" s="33"/>
+      <c r="E183" s="33"/>
+      <c r="F183" s="33"/>
+      <c r="G183" s="33"/>
+      <c r="H183" s="33"/>
+      <c r="I183" s="33"/>
+      <c r="J183" s="33"/>
+      <c r="K183" s="33"/>
+      <c r="L183" s="33"/>
+      <c r="M183" s="33"/>
     </row>
     <row r="184" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B184" s="32"/>
-      <c r="C184" s="32"/>
-      <c r="D184" s="32"/>
-      <c r="E184" s="32"/>
-      <c r="F184" s="32"/>
-      <c r="G184" s="32"/>
-      <c r="H184" s="32"/>
-      <c r="I184" s="32"/>
-      <c r="J184" s="32"/>
-      <c r="K184" s="32"/>
-      <c r="L184" s="32"/>
-      <c r="M184" s="32"/>
+      <c r="B184" s="33"/>
+      <c r="C184" s="33"/>
+      <c r="D184" s="33"/>
+      <c r="E184" s="33"/>
+      <c r="F184" s="33"/>
+      <c r="G184" s="33"/>
+      <c r="H184" s="33"/>
+      <c r="I184" s="33"/>
+      <c r="J184" s="33"/>
+      <c r="K184" s="33"/>
+      <c r="L184" s="33"/>
+      <c r="M184" s="33"/>
     </row>
     <row r="185" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B185" s="32"/>
-      <c r="C185" s="32"/>
-      <c r="D185" s="32"/>
-      <c r="E185" s="32"/>
-      <c r="F185" s="32"/>
-      <c r="G185" s="32"/>
-      <c r="H185" s="32"/>
-      <c r="I185" s="32"/>
-      <c r="J185" s="32"/>
-      <c r="K185" s="32"/>
-      <c r="L185" s="32"/>
-      <c r="M185" s="32"/>
+      <c r="B185" s="33"/>
+      <c r="C185" s="33"/>
+      <c r="D185" s="33"/>
+      <c r="E185" s="33"/>
+      <c r="F185" s="33"/>
+      <c r="G185" s="33"/>
+      <c r="H185" s="33"/>
+      <c r="I185" s="33"/>
+      <c r="J185" s="33"/>
+      <c r="K185" s="33"/>
+      <c r="L185" s="33"/>
+      <c r="M185" s="33"/>
     </row>
     <row r="186" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B186" s="32"/>
-      <c r="C186" s="32"/>
-      <c r="D186" s="32"/>
-      <c r="E186" s="32"/>
-      <c r="F186" s="32"/>
-      <c r="G186" s="32"/>
-      <c r="H186" s="32"/>
-      <c r="I186" s="32"/>
-      <c r="J186" s="32"/>
-      <c r="K186" s="32"/>
-      <c r="L186" s="32"/>
-      <c r="M186" s="32"/>
+      <c r="B186" s="33"/>
+      <c r="C186" s="33"/>
+      <c r="D186" s="33"/>
+      <c r="E186" s="33"/>
+      <c r="F186" s="33"/>
+      <c r="G186" s="33"/>
+      <c r="H186" s="33"/>
+      <c r="I186" s="33"/>
+      <c r="J186" s="33"/>
+      <c r="K186" s="33"/>
+      <c r="L186" s="33"/>
+      <c r="M186" s="33"/>
     </row>
     <row r="187" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B187" s="32"/>
-      <c r="C187" s="32"/>
-      <c r="D187" s="32"/>
-      <c r="E187" s="32"/>
-      <c r="F187" s="32"/>
-      <c r="G187" s="32"/>
-      <c r="H187" s="32"/>
-      <c r="I187" s="32"/>
-      <c r="J187" s="32"/>
-      <c r="K187" s="32"/>
-      <c r="L187" s="32"/>
-      <c r="M187" s="32"/>
+      <c r="B187" s="33"/>
+      <c r="C187" s="33"/>
+      <c r="D187" s="33"/>
+      <c r="E187" s="33"/>
+      <c r="F187" s="33"/>
+      <c r="G187" s="33"/>
+      <c r="H187" s="33"/>
+      <c r="I187" s="33"/>
+      <c r="J187" s="33"/>
+      <c r="K187" s="33"/>
+      <c r="L187" s="33"/>
+      <c r="M187" s="33"/>
     </row>
     <row r="188" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B188" s="32"/>
-      <c r="C188" s="32"/>
-      <c r="D188" s="32"/>
-      <c r="E188" s="32"/>
-      <c r="F188" s="32"/>
-      <c r="G188" s="32"/>
-      <c r="H188" s="32"/>
-      <c r="I188" s="32"/>
-      <c r="J188" s="32"/>
-      <c r="K188" s="32"/>
-      <c r="L188" s="32"/>
-      <c r="M188" s="32"/>
+      <c r="B188" s="33"/>
+      <c r="C188" s="33"/>
+      <c r="D188" s="33"/>
+      <c r="E188" s="33"/>
+      <c r="F188" s="33"/>
+      <c r="G188" s="33"/>
+      <c r="H188" s="33"/>
+      <c r="I188" s="33"/>
+      <c r="J188" s="33"/>
+      <c r="K188" s="33"/>
+      <c r="L188" s="33"/>
+      <c r="M188" s="33"/>
     </row>
     <row r="189" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B189" s="32"/>
-      <c r="C189" s="32"/>
-      <c r="D189" s="32"/>
-      <c r="E189" s="32"/>
-      <c r="F189" s="32"/>
-      <c r="G189" s="32"/>
-      <c r="H189" s="32"/>
-      <c r="I189" s="32"/>
-      <c r="J189" s="32"/>
-      <c r="K189" s="32"/>
-      <c r="L189" s="32"/>
-      <c r="M189" s="32"/>
+      <c r="B189" s="33"/>
+      <c r="C189" s="33"/>
+      <c r="D189" s="33"/>
+      <c r="E189" s="33"/>
+      <c r="F189" s="33"/>
+      <c r="G189" s="33"/>
+      <c r="H189" s="33"/>
+      <c r="I189" s="33"/>
+      <c r="J189" s="33"/>
+      <c r="K189" s="33"/>
+      <c r="L189" s="33"/>
+      <c r="M189" s="33"/>
     </row>
     <row r="190" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B190" s="32"/>
-      <c r="C190" s="32"/>
-      <c r="D190" s="32"/>
-      <c r="E190" s="32"/>
-      <c r="F190" s="32"/>
-      <c r="G190" s="32"/>
-      <c r="H190" s="32"/>
-      <c r="I190" s="32"/>
-      <c r="J190" s="32"/>
-      <c r="K190" s="32"/>
-      <c r="L190" s="32"/>
-      <c r="M190" s="32"/>
+      <c r="B190" s="33"/>
+      <c r="C190" s="33"/>
+      <c r="D190" s="33"/>
+      <c r="E190" s="33"/>
+      <c r="F190" s="33"/>
+      <c r="G190" s="33"/>
+      <c r="H190" s="33"/>
+      <c r="I190" s="33"/>
+      <c r="J190" s="33"/>
+      <c r="K190" s="33"/>
+      <c r="L190" s="33"/>
+      <c r="M190" s="33"/>
     </row>
     <row r="191" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B191" s="32"/>
-      <c r="C191" s="32"/>
-      <c r="D191" s="32"/>
-      <c r="E191" s="32"/>
-      <c r="F191" s="32"/>
-      <c r="G191" s="32"/>
-      <c r="H191" s="32"/>
-      <c r="I191" s="32"/>
-      <c r="J191" s="32"/>
-      <c r="K191" s="32"/>
-      <c r="L191" s="32"/>
-      <c r="M191" s="32"/>
+      <c r="B191" s="33"/>
+      <c r="C191" s="33"/>
+      <c r="D191" s="33"/>
+      <c r="E191" s="33"/>
+      <c r="F191" s="33"/>
+      <c r="G191" s="33"/>
+      <c r="H191" s="33"/>
+      <c r="I191" s="33"/>
+      <c r="J191" s="33"/>
+      <c r="K191" s="33"/>
+      <c r="L191" s="33"/>
+      <c r="M191" s="33"/>
     </row>
     <row r="192" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B192" s="32"/>
-      <c r="C192" s="32"/>
-      <c r="D192" s="32"/>
-      <c r="E192" s="32"/>
-      <c r="F192" s="32"/>
-      <c r="G192" s="32"/>
-      <c r="H192" s="32"/>
-      <c r="I192" s="32"/>
-      <c r="J192" s="32"/>
-      <c r="K192" s="32"/>
-      <c r="L192" s="32"/>
-      <c r="M192" s="32"/>
+      <c r="B192" s="33"/>
+      <c r="C192" s="33"/>
+      <c r="D192" s="33"/>
+      <c r="E192" s="33"/>
+      <c r="F192" s="33"/>
+      <c r="G192" s="33"/>
+      <c r="H192" s="33"/>
+      <c r="I192" s="33"/>
+      <c r="J192" s="33"/>
+      <c r="K192" s="33"/>
+      <c r="L192" s="33"/>
+      <c r="M192" s="33"/>
     </row>
     <row r="193" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B193" s="32"/>
-      <c r="C193" s="32"/>
-      <c r="D193" s="32"/>
-      <c r="E193" s="32"/>
-      <c r="F193" s="32"/>
-      <c r="G193" s="32"/>
-      <c r="H193" s="32"/>
-      <c r="I193" s="32"/>
-      <c r="J193" s="32"/>
-      <c r="K193" s="32"/>
-      <c r="L193" s="32"/>
-      <c r="M193" s="32"/>
+      <c r="B193" s="33"/>
+      <c r="C193" s="33"/>
+      <c r="D193" s="33"/>
+      <c r="E193" s="33"/>
+      <c r="F193" s="33"/>
+      <c r="G193" s="33"/>
+      <c r="H193" s="33"/>
+      <c r="I193" s="33"/>
+      <c r="J193" s="33"/>
+      <c r="K193" s="33"/>
+      <c r="L193" s="33"/>
+      <c r="M193" s="33"/>
     </row>
     <row r="194" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B194" s="32"/>
-      <c r="C194" s="32"/>
-      <c r="D194" s="32"/>
-      <c r="E194" s="32"/>
-      <c r="F194" s="32"/>
-      <c r="G194" s="32"/>
-      <c r="H194" s="32"/>
-      <c r="I194" s="32"/>
-      <c r="J194" s="32"/>
-      <c r="K194" s="32"/>
-      <c r="L194" s="32"/>
-      <c r="M194" s="32"/>
+      <c r="B194" s="33"/>
+      <c r="C194" s="33"/>
+      <c r="D194" s="33"/>
+      <c r="E194" s="33"/>
+      <c r="F194" s="33"/>
+      <c r="G194" s="33"/>
+      <c r="H194" s="33"/>
+      <c r="I194" s="33"/>
+      <c r="J194" s="33"/>
+      <c r="K194" s="33"/>
+      <c r="L194" s="33"/>
+      <c r="M194" s="33"/>
     </row>
     <row r="195" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B195" s="32"/>
-      <c r="C195" s="32"/>
-      <c r="D195" s="32"/>
-      <c r="E195" s="32"/>
-      <c r="F195" s="32"/>
-      <c r="G195" s="32"/>
-      <c r="H195" s="32"/>
-      <c r="I195" s="32"/>
-      <c r="J195" s="32"/>
-      <c r="K195" s="32"/>
-      <c r="L195" s="32"/>
-      <c r="M195" s="32"/>
+      <c r="B195" s="33"/>
+      <c r="C195" s="33"/>
+      <c r="D195" s="33"/>
+      <c r="E195" s="33"/>
+      <c r="F195" s="33"/>
+      <c r="G195" s="33"/>
+      <c r="H195" s="33"/>
+      <c r="I195" s="33"/>
+      <c r="J195" s="33"/>
+      <c r="K195" s="33"/>
+      <c r="L195" s="33"/>
+      <c r="M195" s="33"/>
     </row>
     <row r="196" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B196" s="3"/>
@@ -5517,33 +5508,33 @@
   <sheetData>
     <row r="1" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="37" t="s">
-        <v>133</v>
-      </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
+        <v>130</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
     </row>
     <row r="2" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>136</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5551,10 +5542,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="6"/>
@@ -5565,10 +5556,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="6"/>
@@ -5579,10 +5570,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="6"/>
@@ -5593,10 +5584,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="6"/>
@@ -6614,7 +6605,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="7" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6640,7 +6631,7 @@
     </row>
     <row r="5" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B5" s="17"/>
       <c r="C5" s="16"/>
@@ -6650,7 +6641,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C6" s="18">
         <v>2</v>
@@ -6661,7 +6652,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C7" s="18">
         <v>3</v>
@@ -6673,7 +6664,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C8" s="18">
         <v>3</v>
@@ -6684,7 +6675,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C9" s="18">
         <v>3</v>
@@ -6695,7 +6686,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C10" s="18">
         <v>3</v>
@@ -6706,7 +6697,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C11" s="18">
         <v>2</v>
@@ -6714,7 +6705,7 @@
     </row>
     <row r="12" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="16"/>
@@ -6724,7 +6715,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C13" s="18">
         <v>2</v>
@@ -6735,7 +6726,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C14" s="18">
         <v>2</v>
@@ -6746,7 +6737,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C15" s="18">
         <v>5</v>
@@ -6757,7 +6748,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C16" s="18">
         <v>5</v>
@@ -6768,7 +6759,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C17" s="18">
         <v>3</v>
@@ -6779,7 +6770,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C18" s="18">
         <v>2</v>
@@ -6790,7 +6781,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C19" s="18">
         <v>2</v>
@@ -6801,7 +6792,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C20" s="18">
         <v>3</v>
@@ -6812,7 +6803,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C21" s="18">
         <v>5</v>
@@ -6823,7 +6814,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C22" s="18">
         <v>3</v>
@@ -6834,7 +6825,7 @@
         <v>17</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C23" s="18">
         <v>2</v>
@@ -6845,7 +6836,7 @@
         <v>18</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C24" s="18">
         <v>5</v>
@@ -6856,7 +6847,7 @@
         <v>19</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C25" s="18">
         <v>5</v>
@@ -6867,7 +6858,7 @@
         <v>20</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C26" s="18">
         <v>2</v>
@@ -6878,7 +6869,7 @@
         <v>21</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C27" s="18">
         <v>3</v>
@@ -6889,7 +6880,7 @@
         <v>22</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C28" s="18">
         <v>2</v>
@@ -6900,7 +6891,7 @@
         <v>23</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C29" s="18">
         <v>1</v>
@@ -6908,7 +6899,7 @@
     </row>
     <row r="30" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B30" s="17"/>
       <c r="C30" s="16"/>
@@ -6918,7 +6909,7 @@
         <v>24</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C31" s="18">
         <v>5</v>
@@ -6929,7 +6920,7 @@
         <v>25</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C32" s="18">
         <v>3</v>
@@ -6940,7 +6931,7 @@
         <v>26</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C33" s="18">
         <v>5</v>
@@ -6951,7 +6942,7 @@
         <v>27</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C34" s="18">
         <v>3</v>
@@ -6962,7 +6953,7 @@
         <v>28</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C35" s="18">
         <v>5</v>
@@ -6973,7 +6964,7 @@
         <v>29</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C36" s="18">
         <v>3</v>
@@ -6984,7 +6975,7 @@
         <v>30</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C37" s="18">
         <v>3</v>
@@ -6995,7 +6986,7 @@
         <v>31</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C38" s="18">
         <v>3</v>
@@ -7006,7 +6997,7 @@
         <v>32</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C39" s="18">
         <v>3</v>
@@ -7017,7 +7008,7 @@
         <v>33</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C40" s="18">
         <v>3</v>
@@ -7028,7 +7019,7 @@
         <v>34</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C41" s="18">
         <v>5</v>
@@ -7039,7 +7030,7 @@
         <v>35</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C42" s="18">
         <v>3</v>
@@ -8024,32 +8015,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
     </row>
     <row r="4" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
@@ -8084,18 +8075,18 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="30"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="29"/>
     </row>
     <row r="6" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
@@ -8108,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E6" s="21" t="s">
         <v>15</v>
@@ -8140,7 +8131,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E7" s="21" t="s">
         <v>15</v>
@@ -8172,7 +8163,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E8" s="21" t="s">
         <v>15</v>
@@ -8204,7 +8195,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E9" s="21" t="s">
         <v>22</v>
@@ -8236,7 +8227,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E10" s="21" t="s">
         <v>22</v>
@@ -8268,7 +8259,7 @@
         <v>2</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E11" s="21" t="s">
         <v>22</v>
@@ -8286,7 +8277,7 @@
         <v>2</v>
       </c>
       <c r="J11" s="22" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -8300,7 +8291,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E12" s="21" t="s">
         <v>22</v>
@@ -8318,7 +8309,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="22" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -8331,7 +8322,9 @@
       <c r="C13" s="21">
         <v>2</v>
       </c>
-      <c r="D13" s="22"/>
+      <c r="D13" s="22" t="s">
+        <v>143</v>
+      </c>
       <c r="E13" s="21" t="s">
         <v>22</v>
       </c>
@@ -8347,7 +8340,9 @@
       <c r="I13" s="21">
         <v>2</v>
       </c>
-      <c r="J13" s="22"/>
+      <c r="J13" s="22" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="23"/>
@@ -8367,18 +8362,18 @@
       <c r="J14" s="23"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="28" t="s">
+      <c r="A15" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="29"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="30"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="29"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
@@ -8391,7 +8386,7 @@
         <v>2</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E16" s="21" t="s">
         <v>39</v>
@@ -8409,7 +8404,7 @@
         <v>2</v>
       </c>
       <c r="J16" s="22" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -8423,7 +8418,7 @@
         <v>3</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E17" s="21" t="s">
         <v>39</v>
@@ -8441,7 +8436,7 @@
         <v>3</v>
       </c>
       <c r="J17" s="22" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -8455,7 +8450,7 @@
         <v>3</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E18" s="21" t="s">
         <v>39</v>
@@ -8473,7 +8468,7 @@
         <v>3</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -8487,7 +8482,7 @@
         <v>3</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E19" s="21" t="s">
         <v>39</v>
@@ -8505,7 +8500,7 @@
         <v>3</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -8519,7 +8514,7 @@
         <v>3</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E20" s="21" t="s">
         <v>39</v>
@@ -8537,7 +8532,7 @@
         <v>3</v>
       </c>
       <c r="J20" s="22" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -8558,18 +8553,18 @@
       <c r="J21" s="23"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="28" t="s">
+      <c r="A22" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="29"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="30"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="29"/>
     </row>
     <row r="23" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="21" t="s">
@@ -8581,7 +8576,9 @@
       <c r="C23" s="21">
         <v>5</v>
       </c>
-      <c r="D23" s="22"/>
+      <c r="D23" s="22" t="s">
+        <v>184</v>
+      </c>
       <c r="E23" s="21" t="s">
         <v>52</v>
       </c>
@@ -8611,7 +8608,9 @@
       <c r="C24" s="21">
         <v>3</v>
       </c>
-      <c r="D24" s="22"/>
+      <c r="D24" s="22" t="s">
+        <v>137</v>
+      </c>
       <c r="E24" s="21" t="s">
         <v>52</v>
       </c>
@@ -8709,18 +8708,18 @@
       <c r="J27" s="23"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="B28" s="29"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
-      <c r="J28" s="30"/>
+      <c r="B28" s="31"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="29"/>
     </row>
     <row r="29" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="21" t="s">
@@ -8808,16 +8807,14 @@
       <c r="I31" s="21">
         <v>5</v>
       </c>
-      <c r="J31" s="22" t="s">
-        <v>74</v>
-      </c>
+      <c r="J31" s="22"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" s="22" t="s">
         <v>75</v>
-      </c>
-      <c r="B32" s="22" t="s">
-        <v>76</v>
       </c>
       <c r="C32" s="21">
         <v>3</v>
@@ -8838,16 +8835,14 @@
       <c r="I32" s="21">
         <v>3</v>
       </c>
-      <c r="J32" s="22" t="s">
-        <v>77</v>
-      </c>
+      <c r="J32" s="22"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" s="22" t="s">
         <v>78</v>
-      </c>
-      <c r="B33" s="22" t="s">
-        <v>79</v>
       </c>
       <c r="C33" s="21">
         <v>2</v>
@@ -8868,16 +8863,14 @@
       <c r="I33" s="21">
         <v>2</v>
       </c>
-      <c r="J33" s="22" t="s">
-        <v>77</v>
-      </c>
+      <c r="J33" s="22"/>
     </row>
     <row r="34" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B34" s="22" t="s">
         <v>80</v>
-      </c>
-      <c r="B34" s="22" t="s">
-        <v>81</v>
       </c>
       <c r="C34" s="21">
         <v>5</v>
@@ -8898,14 +8891,12 @@
       <c r="I34" s="21">
         <v>5</v>
       </c>
-      <c r="J34" s="22" t="s">
-        <v>82</v>
-      </c>
+      <c r="J34" s="22"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="23"/>
       <c r="B35" s="24" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C35" s="25">
         <f>SUM(C29:C34)</f>
@@ -8920,203 +8911,199 @@
       <c r="J35" s="23"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="B36" s="29"/>
-      <c r="C36" s="29"/>
-      <c r="D36" s="29"/>
-      <c r="E36" s="29"/>
-      <c r="F36" s="29"/>
-      <c r="G36" s="29"/>
-      <c r="H36" s="29"/>
-      <c r="I36" s="29"/>
-      <c r="J36" s="30"/>
+      <c r="A36" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="B36" s="31"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="31"/>
+      <c r="I36" s="31"/>
+      <c r="J36" s="29"/>
     </row>
     <row r="37" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C37" s="21">
         <v>5</v>
       </c>
       <c r="D37" s="22"/>
       <c r="E37" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F37" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G37" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H37" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I37" s="21">
         <v>5</v>
       </c>
-      <c r="J37" s="22" t="s">
-        <v>88</v>
-      </c>
+      <c r="J37" s="22"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="21" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B38" s="22" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C38" s="21">
         <v>5</v>
       </c>
       <c r="D38" s="22"/>
       <c r="E38" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F38" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G38" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H38" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I38" s="21">
         <v>5</v>
       </c>
-      <c r="J38" s="22" t="s">
-        <v>77</v>
-      </c>
+      <c r="J38" s="22"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C39" s="21">
         <v>3</v>
       </c>
       <c r="D39" s="22"/>
       <c r="E39" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F39" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G39" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H39" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I39" s="21">
         <v>3</v>
       </c>
       <c r="J39" s="22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="21" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B40" s="22" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C40" s="21">
         <v>2</v>
       </c>
       <c r="D40" s="22"/>
       <c r="E40" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F40" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G40" s="21" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H40" s="21" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I40" s="21" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J40" s="22" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="21" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C41" s="21">
         <v>2</v>
       </c>
       <c r="D41" s="22"/>
       <c r="E41" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F41" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G41" s="21" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H41" s="21" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I41" s="21" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J41" s="22" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="21" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B42" s="22" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C42" s="21">
         <v>3</v>
       </c>
       <c r="D42" s="22"/>
       <c r="E42" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F42" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G42" s="21" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H42" s="21" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I42" s="21" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J42" s="22" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="23"/>
       <c r="B43" s="24" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C43" s="25">
         <f>SUM(C37:C42)</f>
@@ -9131,131 +9118,131 @@
       <c r="J43" s="23"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="28" t="s">
-        <v>104</v>
-      </c>
-      <c r="B44" s="29"/>
-      <c r="C44" s="29"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="29"/>
-      <c r="F44" s="29"/>
-      <c r="G44" s="29"/>
-      <c r="H44" s="29"/>
-      <c r="I44" s="29"/>
-      <c r="J44" s="30"/>
+      <c r="A44" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="B44" s="31"/>
+      <c r="C44" s="31"/>
+      <c r="D44" s="31"/>
+      <c r="E44" s="31"/>
+      <c r="F44" s="31"/>
+      <c r="G44" s="31"/>
+      <c r="H44" s="31"/>
+      <c r="I44" s="31"/>
+      <c r="J44" s="29"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="21" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B45" s="22" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C45" s="21">
         <v>2</v>
       </c>
       <c r="D45" s="22"/>
       <c r="E45" s="21" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F45" s="21" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G45" s="21" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H45" s="21" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I45" s="21">
         <v>2</v>
       </c>
       <c r="J45" s="22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="21" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B46" s="22" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C46" s="21">
         <v>3</v>
       </c>
       <c r="D46" s="22"/>
       <c r="E46" s="21" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F46" s="21" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G46" s="21" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H46" s="21" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I46" s="21">
         <v>3</v>
       </c>
       <c r="J46" s="22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="21" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B47" s="22" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C47" s="21">
         <v>2</v>
       </c>
       <c r="D47" s="22"/>
       <c r="E47" s="21" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F47" s="21" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G47" s="21" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H47" s="21" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I47" s="21">
         <v>2</v>
       </c>
       <c r="J47" s="22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="21" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B48" s="22" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C48" s="21">
         <v>3</v>
       </c>
       <c r="D48" s="22"/>
       <c r="E48" s="21" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F48" s="21" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G48" s="21" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H48" s="21" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I48" s="21">
         <v>3</v>
@@ -9264,38 +9251,38 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="21" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C49" s="21">
         <v>3</v>
       </c>
       <c r="D49" s="22"/>
       <c r="E49" s="21" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F49" s="21" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G49" s="21" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H49" s="21" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I49" s="21">
         <v>3</v>
       </c>
       <c r="J49" s="22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="23"/>
       <c r="B50" s="24" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C50" s="25">
         <f>SUM(C45:C49)</f>
@@ -9310,41 +9297,41 @@
       <c r="J50" s="23"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="28" t="s">
-        <v>117</v>
-      </c>
-      <c r="B51" s="29"/>
-      <c r="C51" s="29"/>
-      <c r="D51" s="29"/>
-      <c r="E51" s="29"/>
-      <c r="F51" s="29"/>
-      <c r="G51" s="29"/>
-      <c r="H51" s="29"/>
-      <c r="I51" s="29"/>
-      <c r="J51" s="30"/>
+      <c r="A51" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="B51" s="31"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="31"/>
+      <c r="E51" s="31"/>
+      <c r="F51" s="31"/>
+      <c r="G51" s="31"/>
+      <c r="H51" s="31"/>
+      <c r="I51" s="31"/>
+      <c r="J51" s="29"/>
     </row>
     <row r="52" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="21" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B52" s="22" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C52" s="21">
         <v>3</v>
       </c>
       <c r="D52" s="22"/>
       <c r="E52" s="21" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F52" s="21" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G52" s="21" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H52" s="21" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I52" s="21">
         <v>3</v>
@@ -9353,26 +9340,26 @@
     </row>
     <row r="53" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="21" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B53" s="22" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C53" s="21">
         <v>3</v>
       </c>
       <c r="D53" s="22"/>
       <c r="E53" s="21" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F53" s="21" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G53" s="21" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H53" s="21" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I53" s="21">
         <v>3</v>
@@ -9381,26 +9368,26 @@
     </row>
     <row r="54" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="21" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B54" s="22" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C54" s="21">
         <v>3</v>
       </c>
       <c r="D54" s="22"/>
       <c r="E54" s="21" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F54" s="21" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G54" s="21" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H54" s="21" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I54" s="21">
         <v>3</v>
@@ -9409,26 +9396,26 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="21" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B55" s="22" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C55" s="21">
         <v>5</v>
       </c>
       <c r="D55" s="22"/>
       <c r="E55" s="21" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F55" s="21" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G55" s="21" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H55" s="21" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I55" s="21">
         <v>5</v>
@@ -9437,26 +9424,26 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="21" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B56" s="22" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C56" s="21">
         <v>3</v>
       </c>
       <c r="D56" s="22"/>
       <c r="E56" s="21" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F56" s="21" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G56" s="21" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H56" s="21" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I56" s="21">
         <v>3</v>
@@ -9466,7 +9453,7 @@
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="23"/>
       <c r="B57" s="24" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C57" s="25">
         <f>SUM(C52:C56)</f>
@@ -9481,10 +9468,10 @@
       <c r="J57" s="23"/>
     </row>
     <row r="58" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="B58" s="30"/>
+      <c r="A58" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="B58" s="29"/>
       <c r="C58" s="26">
         <f>C14+C21+C27+C35+C43+C50+C57</f>
         <v>116</v>

--- a/Docx/ProductBacklog-Nhom7.xlsx
+++ b/Docx/ProductBacklog-Nhom7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9756614-111E-4E63-9182-32AAE49B30DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{251C8EF3-4213-47FB-B6CE-D3C2AB6BEC18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="190">
   <si>
     <t>STORY READER SYSTEM - SPRINT BACKLOG</t>
   </si>
@@ -741,6 +741,18 @@
   </si>
   <si>
     <t>Đã xong [x] Backend + Web + Mobile</t>
+  </si>
+  <si>
+    <t>Lê Hoàng + Trần Minh Tuyên</t>
+  </si>
+  <si>
+    <t>Trần Mỹ Duyên + Hồ Minh Tuyền</t>
+  </si>
+  <si>
+    <t>Trần Minh Tuyên + Lê Hoàng</t>
+  </si>
+  <si>
+    <t>Hồ Minh Tuyền + Trần Mỹ Duyên</t>
   </si>
 </sst>
 </file>
@@ -8007,7 +8019,7 @@
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="48" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="4" max="4" width="30.109375" customWidth="1"/>
     <col min="5" max="6" width="11" customWidth="1"/>
     <col min="7" max="8" width="13" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
@@ -8099,7 +8111,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E6" s="21" t="s">
         <v>15</v>
@@ -8323,7 +8335,7 @@
         <v>2</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="E13" s="21" t="s">
         <v>22</v>
@@ -8386,7 +8398,7 @@
         <v>2</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>141</v>
+        <v>189</v>
       </c>
       <c r="E16" s="21" t="s">
         <v>39</v>
@@ -8418,7 +8430,7 @@
         <v>3</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="E17" s="21" t="s">
         <v>39</v>

--- a/Docx/ProductBacklog-Nhom7.xlsx
+++ b/Docx/ProductBacklog-Nhom7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{251C8EF3-4213-47FB-B6CE-D3C2AB6BEC18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D55C88F3-5A28-4B2A-9271-CF5FD6DD9FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,14 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="186">
   <si>
     <t>STORY READER SYSTEM - SPRINT BACKLOG</t>
   </si>
   <si>
-    <t>* Tuần 1-2: Requirements/Product Backlog. Tuần 3-4 (Sprint 0): vừa hoàn thiện Product Backlog/Sprint Backlog/PERT/Sprint Planning vừa dựng hạ tầng + code REST API (C#) + Auth. Cột "Name Of Dev" điền sau khi nhóm họp phân công.</t>
-  </si>
-  <si>
     <t>Story ID</t>
   </si>
   <si>
@@ -239,18 +236,12 @@
     <t>Tuần 7</t>
   </si>
   <si>
-    <t>Đã xong Backend [x] | Có thể tạo mới/đổi phí/đổi phạm vi hoặc ngừng cung cấp gói</t>
-  </si>
-  <si>
     <t>PB27</t>
   </si>
   <si>
     <t>Manage Story Pricing (Admin) - Thiết lập giá truyện</t>
   </si>
   <si>
-    <t>Đã xong Backend [x] | Giá áp dụng TẠI THỜI ĐIỂM giao dịch, không hồi tố</t>
-  </si>
-  <si>
     <t>PB15</t>
   </si>
   <si>
@@ -264,9 +255,6 @@
   </si>
   <si>
     <t>Renew Monthly Package - Gia hạn gói đọc</t>
-  </si>
-  <si>
-    <t>Đã xong Backend [x]</t>
   </si>
   <si>
     <t>PB17</t>
@@ -1344,7 +1332,7 @@
     <row r="1" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1354,7 +1342,7 @@
     </row>
     <row r="4" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="35" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C4" s="36"/>
       <c r="D4" s="36"/>
@@ -5520,7 +5508,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="37" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
@@ -5531,22 +5519,22 @@
     <row r="2" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>132</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5554,10 +5542,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="6"/>
@@ -5568,10 +5556,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="6"/>
@@ -5582,10 +5570,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="6"/>
@@ -5596,10 +5584,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="6"/>
@@ -6617,7 +6605,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="7" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6627,13 +6615,13 @@
     </row>
     <row r="3" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="C3" s="12" t="s">
         <v>3</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6643,7 +6631,7 @@
     </row>
     <row r="5" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B5" s="17"/>
       <c r="C5" s="16"/>
@@ -6653,7 +6641,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C6" s="18">
         <v>2</v>
@@ -6664,7 +6652,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C7" s="18">
         <v>3</v>
@@ -6676,7 +6664,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C8" s="18">
         <v>3</v>
@@ -6687,7 +6675,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C9" s="18">
         <v>3</v>
@@ -6698,7 +6686,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C10" s="18">
         <v>3</v>
@@ -6709,7 +6697,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C11" s="18">
         <v>2</v>
@@ -6717,7 +6705,7 @@
     </row>
     <row r="12" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="16"/>
@@ -6727,7 +6715,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C13" s="18">
         <v>2</v>
@@ -6738,7 +6726,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C14" s="18">
         <v>2</v>
@@ -6749,7 +6737,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C15" s="18">
         <v>5</v>
@@ -6760,7 +6748,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C16" s="18">
         <v>5</v>
@@ -6771,7 +6759,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C17" s="18">
         <v>3</v>
@@ -6782,7 +6770,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C18" s="18">
         <v>2</v>
@@ -6793,7 +6781,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C19" s="18">
         <v>2</v>
@@ -6804,7 +6792,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C20" s="18">
         <v>3</v>
@@ -6815,7 +6803,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C21" s="18">
         <v>5</v>
@@ -6826,7 +6814,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C22" s="18">
         <v>3</v>
@@ -6837,7 +6825,7 @@
         <v>17</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C23" s="18">
         <v>2</v>
@@ -6848,7 +6836,7 @@
         <v>18</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C24" s="18">
         <v>5</v>
@@ -6859,7 +6847,7 @@
         <v>19</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C25" s="18">
         <v>5</v>
@@ -6870,7 +6858,7 @@
         <v>20</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C26" s="18">
         <v>2</v>
@@ -6881,7 +6869,7 @@
         <v>21</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C27" s="18">
         <v>3</v>
@@ -6892,7 +6880,7 @@
         <v>22</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C28" s="18">
         <v>2</v>
@@ -6903,7 +6891,7 @@
         <v>23</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C29" s="18">
         <v>1</v>
@@ -6911,7 +6899,7 @@
     </row>
     <row r="30" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B30" s="17"/>
       <c r="C30" s="16"/>
@@ -6921,7 +6909,7 @@
         <v>24</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C31" s="18">
         <v>5</v>
@@ -6932,7 +6920,7 @@
         <v>25</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C32" s="18">
         <v>3</v>
@@ -6943,7 +6931,7 @@
         <v>26</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C33" s="18">
         <v>5</v>
@@ -6954,7 +6942,7 @@
         <v>27</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C34" s="18">
         <v>3</v>
@@ -6965,7 +6953,7 @@
         <v>28</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C35" s="18">
         <v>5</v>
@@ -6976,7 +6964,7 @@
         <v>29</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C36" s="18">
         <v>3</v>
@@ -6987,7 +6975,7 @@
         <v>30</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C37" s="18">
         <v>3</v>
@@ -6998,7 +6986,7 @@
         <v>31</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C38" s="18">
         <v>3</v>
@@ -7009,7 +6997,7 @@
         <v>32</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C39" s="18">
         <v>3</v>
@@ -7020,7 +7008,7 @@
         <v>33</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C40" s="18">
         <v>3</v>
@@ -7031,7 +7019,7 @@
         <v>34</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C41" s="18">
         <v>5</v>
@@ -7042,7 +7030,7 @@
         <v>35</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C42" s="18">
         <v>3</v>
@@ -8041,9 +8029,7 @@
       <c r="J1" s="33"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
-        <v>1</v>
-      </c>
+      <c r="A2" s="34"/>
       <c r="B2" s="33"/>
       <c r="C2" s="33"/>
       <c r="D2" s="33"/>
@@ -8056,39 +8042,39 @@
     </row>
     <row r="4" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="C4" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="D4" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="E4" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="F4" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="G4" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="H4" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="20" t="s">
+      <c r="I4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="20" t="s">
+      <c r="J4" s="20" t="s">
         <v>10</v>
-      </c>
-      <c r="J4" s="20" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="31"/>
       <c r="C5" s="31"/>
@@ -8102,264 +8088,264 @@
     </row>
     <row r="6" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="22" t="s">
         <v>13</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>14</v>
       </c>
       <c r="C6" s="21">
         <v>1</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I6" s="21">
         <v>1</v>
       </c>
       <c r="J6" s="22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="22" t="s">
         <v>17</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>18</v>
       </c>
       <c r="C7" s="21">
         <v>1</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I7" s="21">
         <v>1</v>
       </c>
       <c r="J7" s="22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="22" t="s">
         <v>20</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>21</v>
       </c>
       <c r="C8" s="21">
         <v>1</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I8" s="21">
         <v>1</v>
       </c>
       <c r="J8" s="22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="22" t="s">
         <v>23</v>
-      </c>
-      <c r="B9" s="22" t="s">
-        <v>24</v>
       </c>
       <c r="C9" s="21">
         <v>1</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I9" s="21">
         <v>1</v>
       </c>
       <c r="J9" s="22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="22" t="s">
         <v>26</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>27</v>
       </c>
       <c r="C10" s="21">
         <v>2</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I10" s="21">
         <v>2</v>
       </c>
       <c r="J10" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="22" t="s">
         <v>29</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>30</v>
       </c>
       <c r="C11" s="21">
         <v>2</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I11" s="21">
         <v>2</v>
       </c>
       <c r="J11" s="22" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="22" t="s">
         <v>31</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>32</v>
       </c>
       <c r="C12" s="21">
         <v>1</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I12" s="21">
         <v>1</v>
       </c>
       <c r="J12" s="22" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="22" t="s">
         <v>33</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>34</v>
       </c>
       <c r="C13" s="21">
         <v>2</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I13" s="21">
         <v>2</v>
       </c>
       <c r="J13" s="22" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="23"/>
       <c r="B14" s="24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" s="25">
         <f>SUM(C6:C13)</f>
@@ -8375,7 +8361,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B15" s="31"/>
       <c r="C15" s="31"/>
@@ -8389,168 +8375,168 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="22" t="s">
         <v>37</v>
-      </c>
-      <c r="B16" s="22" t="s">
-        <v>38</v>
       </c>
       <c r="C16" s="21">
         <v>2</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G16" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I16" s="21">
         <v>2</v>
       </c>
       <c r="J16" s="22" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="22" t="s">
         <v>40</v>
-      </c>
-      <c r="B17" s="22" t="s">
-        <v>41</v>
       </c>
       <c r="C17" s="21">
         <v>3</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="E17" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F17" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G17" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H17" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I17" s="21">
         <v>3</v>
       </c>
       <c r="J17" s="22" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="22" t="s">
         <v>42</v>
-      </c>
-      <c r="B18" s="22" t="s">
-        <v>43</v>
       </c>
       <c r="C18" s="21">
         <v>3</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G18" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H18" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I18" s="21">
         <v>3</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="22" t="s">
         <v>44</v>
-      </c>
-      <c r="B19" s="22" t="s">
-        <v>45</v>
       </c>
       <c r="C19" s="21">
         <v>3</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G19" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I19" s="21">
         <v>3</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="22" t="s">
         <v>46</v>
-      </c>
-      <c r="B20" s="22" t="s">
-        <v>47</v>
       </c>
       <c r="C20" s="21">
         <v>3</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G20" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H20" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I20" s="21">
         <v>3</v>
       </c>
       <c r="J20" s="22" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="23"/>
       <c r="B21" s="24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C21" s="25">
         <f>SUM(C16:C20)</f>
@@ -8566,7 +8552,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="30" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B22" s="31"/>
       <c r="C22" s="31"/>
@@ -8580,132 +8566,132 @@
     </row>
     <row r="23" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="22" t="s">
         <v>50</v>
-      </c>
-      <c r="B23" s="22" t="s">
-        <v>51</v>
       </c>
       <c r="C23" s="21">
         <v>5</v>
       </c>
       <c r="D23" s="22" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F23" s="21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G23" s="21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H23" s="21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I23" s="21">
         <v>5</v>
       </c>
       <c r="J23" s="22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="22" t="s">
         <v>54</v>
-      </c>
-      <c r="B24" s="22" t="s">
-        <v>55</v>
       </c>
       <c r="C24" s="21">
         <v>3</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G24" s="21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H24" s="21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I24" s="21">
         <v>3</v>
       </c>
       <c r="J24" s="22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="22" t="s">
         <v>56</v>
-      </c>
-      <c r="B25" s="22" t="s">
-        <v>57</v>
       </c>
       <c r="C25" s="21">
         <v>5</v>
       </c>
       <c r="D25" s="22"/>
       <c r="E25" s="21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G25" s="21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H25" s="21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I25" s="21">
         <v>5</v>
       </c>
       <c r="J25" s="22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="22" t="s">
         <v>59</v>
-      </c>
-      <c r="B26" s="22" t="s">
-        <v>60</v>
       </c>
       <c r="C26" s="21">
         <v>5</v>
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G26" s="21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H26" s="21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I26" s="21">
         <v>5</v>
       </c>
       <c r="J26" s="22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="23"/>
       <c r="B27" s="24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C27" s="25">
         <f>SUM(C23:C26)</f>
@@ -8721,7 +8707,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B28" s="31"/>
       <c r="C28" s="31"/>
@@ -8735,86 +8721,82 @@
     </row>
     <row r="29" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B29" s="22" t="s">
         <v>64</v>
-      </c>
-      <c r="B29" s="22" t="s">
-        <v>65</v>
       </c>
       <c r="C29" s="21">
         <v>5</v>
       </c>
       <c r="D29" s="22"/>
       <c r="E29" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F29" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G29" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H29" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I29" s="21">
         <v>5</v>
       </c>
-      <c r="J29" s="22" t="s">
-        <v>67</v>
-      </c>
+      <c r="J29" s="22"/>
     </row>
     <row r="30" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="21" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C30" s="21">
         <v>3</v>
       </c>
       <c r="D30" s="22"/>
       <c r="E30" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F30" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G30" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H30" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I30" s="21">
         <v>3</v>
       </c>
-      <c r="J30" s="22" t="s">
-        <v>70</v>
-      </c>
+      <c r="J30" s="22"/>
     </row>
     <row r="31" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="21" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C31" s="21">
         <v>5</v>
       </c>
       <c r="D31" s="22"/>
       <c r="E31" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F31" s="21" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G31" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H31" s="21" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I31" s="21">
         <v>5</v>
@@ -8823,26 +8805,26 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="21" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C32" s="21">
         <v>3</v>
       </c>
       <c r="D32" s="22"/>
       <c r="E32" s="21" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F32" s="21" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G32" s="21" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H32" s="21" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I32" s="21">
         <v>3</v>
@@ -8851,26 +8833,26 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="21" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C33" s="21">
         <v>2</v>
       </c>
       <c r="D33" s="22"/>
       <c r="E33" s="21" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F33" s="21" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G33" s="21" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H33" s="21" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I33" s="21">
         <v>2</v>
@@ -8879,26 +8861,26 @@
     </row>
     <row r="34" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="21" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B34" s="22" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C34" s="21">
         <v>5</v>
       </c>
       <c r="D34" s="22"/>
       <c r="E34" s="21" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F34" s="21" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G34" s="21" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H34" s="21" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I34" s="21">
         <v>5</v>
@@ -8908,7 +8890,7 @@
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="23"/>
       <c r="B35" s="24" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C35" s="25">
         <f>SUM(C29:C34)</f>
@@ -8924,7 +8906,7 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="30" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B36" s="31"/>
       <c r="C36" s="31"/>
@@ -8938,26 +8920,26 @@
     </row>
     <row r="37" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="21" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C37" s="21">
         <v>5</v>
       </c>
       <c r="D37" s="22"/>
       <c r="E37" s="21" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F37" s="21" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G37" s="21" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H37" s="21" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="I37" s="21">
         <v>5</v>
@@ -8966,26 +8948,26 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="21" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B38" s="22" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C38" s="21">
         <v>5</v>
       </c>
       <c r="D38" s="22"/>
       <c r="E38" s="21" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F38" s="21" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G38" s="21" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H38" s="21" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="I38" s="21">
         <v>5</v>
@@ -8994,128 +8976,126 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C39" s="21">
         <v>3</v>
       </c>
       <c r="D39" s="22"/>
       <c r="E39" s="21" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F39" s="21" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G39" s="21" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H39" s="21" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="I39" s="21">
         <v>3</v>
       </c>
-      <c r="J39" s="22" t="s">
-        <v>76</v>
-      </c>
+      <c r="J39" s="22"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="21" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B40" s="22" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C40" s="21">
         <v>2</v>
       </c>
       <c r="D40" s="22"/>
       <c r="E40" s="21" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F40" s="21" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G40" s="21" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H40" s="21" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I40" s="21" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="J40" s="22" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="21" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C41" s="21">
         <v>2</v>
       </c>
       <c r="D41" s="22"/>
       <c r="E41" s="21" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F41" s="21" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G41" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="H41" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="I41" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="J41" s="22" t="s">
         <v>92</v>
-      </c>
-      <c r="H41" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="I41" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="J41" s="22" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="21" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B42" s="22" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C42" s="21">
         <v>3</v>
       </c>
       <c r="D42" s="22"/>
       <c r="E42" s="21" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F42" s="21" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G42" s="21" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H42" s="21" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I42" s="21" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="J42" s="22" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="23"/>
       <c r="B43" s="24" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C43" s="25">
         <f>SUM(C37:C42)</f>
@@ -9131,7 +9111,7 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="30" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B44" s="31"/>
       <c r="C44" s="31"/>
@@ -9145,116 +9125,110 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="21" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B45" s="22" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C45" s="21">
         <v>2</v>
       </c>
       <c r="D45" s="22"/>
       <c r="E45" s="21" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F45" s="21" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G45" s="21" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H45" s="21" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I45" s="21">
         <v>2</v>
       </c>
-      <c r="J45" s="22" t="s">
-        <v>76</v>
-      </c>
+      <c r="J45" s="22"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="21" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B46" s="22" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C46" s="21">
         <v>3</v>
       </c>
       <c r="D46" s="22"/>
       <c r="E46" s="21" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F46" s="21" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G46" s="21" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H46" s="21" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I46" s="21">
         <v>3</v>
       </c>
-      <c r="J46" s="22" t="s">
-        <v>76</v>
-      </c>
+      <c r="J46" s="22"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="21" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B47" s="22" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C47" s="21">
         <v>2</v>
       </c>
       <c r="D47" s="22"/>
       <c r="E47" s="21" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F47" s="21" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G47" s="21" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H47" s="21" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I47" s="21">
         <v>2</v>
       </c>
-      <c r="J47" s="22" t="s">
-        <v>76</v>
-      </c>
+      <c r="J47" s="22"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="21" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B48" s="22" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C48" s="21">
         <v>3</v>
       </c>
       <c r="D48" s="22"/>
       <c r="E48" s="21" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F48" s="21" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G48" s="21" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H48" s="21" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I48" s="21">
         <v>3</v>
@@ -9263,38 +9237,36 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="21" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C49" s="21">
         <v>3</v>
       </c>
       <c r="D49" s="22"/>
       <c r="E49" s="21" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F49" s="21" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G49" s="21" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H49" s="21" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I49" s="21">
         <v>3</v>
       </c>
-      <c r="J49" s="22" t="s">
-        <v>76</v>
-      </c>
+      <c r="J49" s="22"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="23"/>
       <c r="B50" s="24" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C50" s="25">
         <f>SUM(C45:C49)</f>
@@ -9310,7 +9282,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="30" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B51" s="31"/>
       <c r="C51" s="31"/>
@@ -9324,26 +9296,26 @@
     </row>
     <row r="52" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="21" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B52" s="22" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C52" s="21">
         <v>3</v>
       </c>
       <c r="D52" s="22"/>
       <c r="E52" s="21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F52" s="21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G52" s="21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H52" s="21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I52" s="21">
         <v>3</v>
@@ -9352,26 +9324,26 @@
     </row>
     <row r="53" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="21" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B53" s="22" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C53" s="21">
         <v>3</v>
       </c>
       <c r="D53" s="22"/>
       <c r="E53" s="21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F53" s="21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G53" s="21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H53" s="21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I53" s="21">
         <v>3</v>
@@ -9380,26 +9352,26 @@
     </row>
     <row r="54" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="21" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B54" s="22" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C54" s="21">
         <v>3</v>
       </c>
       <c r="D54" s="22"/>
       <c r="E54" s="21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F54" s="21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G54" s="21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H54" s="21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I54" s="21">
         <v>3</v>
@@ -9408,26 +9380,26 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="21" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B55" s="22" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C55" s="21">
         <v>5</v>
       </c>
       <c r="D55" s="22"/>
       <c r="E55" s="21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F55" s="21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G55" s="21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H55" s="21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I55" s="21">
         <v>5</v>
@@ -9436,26 +9408,26 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="21" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B56" s="22" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C56" s="21">
         <v>3</v>
       </c>
       <c r="D56" s="22"/>
       <c r="E56" s="21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F56" s="21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G56" s="21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H56" s="21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I56" s="21">
         <v>3</v>
@@ -9465,7 +9437,7 @@
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="23"/>
       <c r="B57" s="24" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C57" s="25">
         <f>SUM(C52:C56)</f>
@@ -9481,7 +9453,7 @@
     </row>
     <row r="58" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="28" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B58" s="29"/>
       <c r="C58" s="26">
